--- a/data/kgv_5y_real.xlsx
+++ b/data/kgv_5y_real.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E909"/>
+  <dimension ref="A1:E908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11415,7 +11415,7 @@
         <v>280.51</v>
       </c>
       <c r="E622" t="n">
-        <v>122.15</v>
+        <v>124.89</v>
       </c>
     </row>
     <row r="623">
@@ -12047,4621 +12047,4602 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US09857L1089</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>23.96</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="C657" t="n">
-        <v>20.86</v>
+        <v>26.4</v>
       </c>
       <c r="D657" t="n">
-        <v>22.24</v>
+        <v>30.21</v>
       </c>
       <c r="E657" t="n">
-        <v>24.4</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>US09857L1089</t>
+          <t>US1011371077</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>85.18000000000001</v>
+        <v>61.83</v>
       </c>
       <c r="C658" t="n">
-        <v>26.4</v>
+        <v>103.77</v>
       </c>
       <c r="D658" t="n">
-        <v>30.21</v>
+        <v>53.89</v>
       </c>
       <c r="E658" t="n">
-        <v>28.77</v>
+        <v>71.62</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>US1011371077</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>61.83</v>
+        <v>20.01</v>
       </c>
       <c r="C659" t="n">
-        <v>103.77</v>
+        <v>24.4</v>
       </c>
       <c r="D659" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="E659" t="n">
-        <v>71.62</v>
-      </c>
+        <v>13.29</v>
+      </c>
+      <c r="E659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US11135F1012</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>20.01</v>
+        <v>35.43</v>
       </c>
       <c r="C660" t="n">
-        <v>24.4</v>
+        <v>17.82</v>
       </c>
       <c r="D660" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="E660" t="inlineStr"/>
+        <v>25.42</v>
+      </c>
+      <c r="E660" t="n">
+        <v>136.91</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>US11135F1012</t>
+          <t>US12541W2098</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>35.43</v>
+        <v>17.06</v>
       </c>
       <c r="C661" t="n">
-        <v>17.82</v>
+        <v>12.38</v>
       </c>
       <c r="D661" t="n">
-        <v>25.42</v>
+        <v>31.8</v>
       </c>
       <c r="E661" t="n">
-        <v>136.91</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>US12541W2098</t>
+          <t>US1255231003</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>17.06</v>
+        <v>14.59</v>
       </c>
       <c r="C662" t="n">
-        <v>12.38</v>
+        <v>15.56</v>
       </c>
       <c r="D662" t="n">
-        <v>31.8</v>
+        <v>17.22</v>
       </c>
       <c r="E662" t="n">
-        <v>26.77</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>US1255231003</t>
+          <t>US12572Q1058</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>14.59</v>
+        <v>31.33</v>
       </c>
       <c r="C663" t="n">
-        <v>15.56</v>
+        <v>22.73</v>
       </c>
       <c r="D663" t="n">
-        <v>17.22</v>
+        <v>23.77</v>
       </c>
       <c r="E663" t="n">
-        <v>22.77</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>US12572Q1058</t>
+          <t>US1258961002</t>
         </is>
       </c>
       <c r="B664" t="n">
-        <v>31.33</v>
+        <v>13.97</v>
       </c>
       <c r="C664" t="n">
-        <v>22.73</v>
+        <v>22.21</v>
       </c>
       <c r="D664" t="n">
-        <v>23.77</v>
+        <v>19.31</v>
       </c>
       <c r="E664" t="n">
-        <v>24.01</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>US1258961002</t>
+          <t>US1264081035</t>
         </is>
       </c>
       <c r="B665" t="n">
-        <v>13.97</v>
+        <v>22.43</v>
       </c>
       <c r="C665" t="n">
-        <v>22.21</v>
+        <v>15.92</v>
       </c>
       <c r="D665" t="n">
-        <v>19.31</v>
+        <v>18.79</v>
       </c>
       <c r="E665" t="n">
-        <v>20.02</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>US1264081035</t>
+          <t>US1266501006</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>22.43</v>
+        <v>17.33</v>
       </c>
       <c r="C666" t="n">
-        <v>15.92</v>
+        <v>29.72</v>
       </c>
       <c r="D666" t="n">
-        <v>18.79</v>
+        <v>12.21</v>
       </c>
       <c r="E666" t="n">
-        <v>18.07</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>US1266501006</t>
+          <t>US1273871087</t>
         </is>
       </c>
       <c r="B667" t="n">
-        <v>17.33</v>
+        <v>74.67</v>
       </c>
       <c r="C667" t="n">
-        <v>29.72</v>
+        <v>52.04</v>
       </c>
       <c r="D667" t="n">
-        <v>12.21</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E667" t="n">
-        <v>12.28</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>US1273871087</t>
+          <t>US1344291091</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>74.67</v>
+        <v>13.31</v>
       </c>
       <c r="C668" t="n">
-        <v>52.04</v>
+        <v>19.69</v>
       </c>
       <c r="D668" t="n">
-        <v>71.34999999999999</v>
+        <v>16.23</v>
       </c>
       <c r="E668" t="n">
-        <v>77.95</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>US1344291091</t>
+          <t>US14448C1045</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>13.31</v>
+        <v>29.02</v>
       </c>
       <c r="C669" t="n">
-        <v>19.69</v>
+        <v>10.05</v>
       </c>
       <c r="D669" t="n">
-        <v>16.23</v>
+        <v>36.33</v>
       </c>
       <c r="E669" t="n">
-        <v>24.74</v>
+        <v>145.42</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>US14448C1045</t>
+          <t>US1491231015</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>29.02</v>
+        <v>17.48</v>
       </c>
       <c r="C670" t="n">
-        <v>10.05</v>
+        <v>18.95</v>
       </c>
       <c r="D670" t="n">
-        <v>36.33</v>
+        <v>14.69</v>
       </c>
       <c r="E670" t="n">
-        <v>145.42</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>US1491231015</t>
+          <t>US16119P1084</t>
         </is>
       </c>
       <c r="B671" t="n">
-        <v>17.48</v>
+        <v>27.04</v>
       </c>
       <c r="C671" t="n">
-        <v>18.95</v>
+        <v>11.03</v>
       </c>
       <c r="D671" t="n">
-        <v>14.69</v>
+        <v>12.96</v>
       </c>
       <c r="E671" t="n">
-        <v>16.45</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>US16119P1084</t>
+          <t>US1651677353</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>27.04</v>
+        <v>1.2</v>
       </c>
       <c r="C672" t="n">
-        <v>11.03</v>
+        <v>2.83</v>
       </c>
       <c r="D672" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E672" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>4.55</v>
+      </c>
+      <c r="E672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>US1651677353</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="B673" t="n">
-        <v>1.2</v>
+        <v>14.42</v>
       </c>
       <c r="C673" t="n">
-        <v>2.83</v>
+        <v>9.82</v>
       </c>
       <c r="D673" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E673" t="inlineStr"/>
+        <v>13.12</v>
+      </c>
+      <c r="E673" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US1696561059</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>14.42</v>
+        <v>76.33</v>
       </c>
       <c r="C674" t="n">
-        <v>9.82</v>
+        <v>43.3</v>
       </c>
       <c r="D674" t="n">
-        <v>13.12</v>
+        <v>51.57</v>
       </c>
       <c r="E674" t="n">
-        <v>14.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>US1696561059</t>
+          <t>US1713401024</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>76.33</v>
+        <v>30.92</v>
       </c>
       <c r="C675" t="n">
-        <v>43.3</v>
+        <v>47.97</v>
       </c>
       <c r="D675" t="n">
-        <v>51.57</v>
+        <v>30.99</v>
       </c>
       <c r="E675" t="n">
-        <v>54.1</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>US1713401024</t>
+          <t>US1717793095</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>30.92</v>
+        <v>17.01</v>
       </c>
       <c r="C676" t="n">
-        <v>47.97</v>
+        <v>48.02</v>
       </c>
       <c r="D676" t="n">
-        <v>30.99</v>
+        <v>24.05</v>
       </c>
       <c r="E676" t="n">
-        <v>44.17</v>
+        <v>111.21</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>US1717793095</t>
+          <t>US17275R1023</t>
         </is>
       </c>
       <c r="B677" t="n">
-        <v>17.01</v>
+        <v>22.15</v>
       </c>
       <c r="C677" t="n">
-        <v>48.02</v>
+        <v>16.1</v>
       </c>
       <c r="D677" t="n">
-        <v>24.05</v>
+        <v>16.95</v>
       </c>
       <c r="E677" t="n">
-        <v>111.21</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>US17275R1023</t>
+          <t>US1729081059</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>22.15</v>
+        <v>34.51</v>
       </c>
       <c r="C678" t="n">
-        <v>16.1</v>
+        <v>34.18</v>
       </c>
       <c r="D678" t="n">
-        <v>16.95</v>
+        <v>36.36</v>
       </c>
       <c r="E678" t="n">
-        <v>18.85</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>US1729081059</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>34.51</v>
+        <v>5.95</v>
       </c>
       <c r="C679" t="n">
-        <v>34.18</v>
+        <v>6.47</v>
       </c>
       <c r="D679" t="n">
-        <v>36.36</v>
+        <v>12.72</v>
       </c>
       <c r="E679" t="n">
-        <v>44.76</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US1890541097</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>5.95</v>
+        <v>32.26</v>
       </c>
       <c r="C680" t="n">
-        <v>6.47</v>
+        <v>37.81</v>
       </c>
       <c r="D680" t="n">
-        <v>12.72</v>
+        <v>132.54</v>
       </c>
       <c r="E680" t="n">
-        <v>11.84</v>
+        <v>60.83</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>US1890541097</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>32.26</v>
+        <v>26.3</v>
       </c>
       <c r="C681" t="n">
-        <v>37.81</v>
+        <v>29</v>
       </c>
       <c r="D681" t="n">
-        <v>132.54</v>
+        <v>23.87</v>
       </c>
       <c r="E681" t="n">
-        <v>60.83</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>US1912161007</t>
-        </is>
-      </c>
-      <c r="B682" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="C682" t="n">
-        <v>29</v>
-      </c>
-      <c r="D682" t="n">
-        <v>23.87</v>
-      </c>
+          <t>US1921085049</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" t="inlineStr"/>
+      <c r="D682" t="inlineStr"/>
       <c r="E682" t="n">
-        <v>25.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>US1921085049</t>
-        </is>
-      </c>
-      <c r="B683" t="inlineStr"/>
-      <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
+          <t>US1924461023</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="C683" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="D683" t="n">
+        <v>17.94</v>
+      </c>
       <c r="E683" t="n">
-        <v>38.6</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>US1924461023</t>
+          <t>US19260Q1076</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>21.92</v>
-      </c>
-      <c r="C684" t="n">
-        <v>12.96</v>
-      </c>
+        <v>17.69</v>
+      </c>
+      <c r="C684" t="inlineStr"/>
       <c r="D684" t="n">
-        <v>17.94</v>
+        <v>466.9</v>
       </c>
       <c r="E684" t="n">
-        <v>17.06</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>US19260Q1076</t>
+          <t>US1941621039</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="C685" t="inlineStr"/>
+        <v>33.42</v>
+      </c>
+      <c r="C685" t="n">
+        <v>37.03</v>
+      </c>
       <c r="D685" t="n">
-        <v>466.9</v>
+        <v>28.74</v>
       </c>
       <c r="E685" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>US1941621039</t>
+          <t>US20030N1019</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>33.42</v>
+        <v>16.54</v>
       </c>
       <c r="C686" t="n">
-        <v>37.03</v>
+        <v>28.85</v>
       </c>
       <c r="D686" t="n">
-        <v>28.74</v>
+        <v>11.82</v>
       </c>
       <c r="E686" t="n">
-        <v>25.9</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>US20030N1019</t>
+          <t>US20825C1045</t>
         </is>
       </c>
       <c r="B687" t="n">
-        <v>16.54</v>
+        <v>11.87</v>
       </c>
       <c r="C687" t="n">
-        <v>28.85</v>
+        <v>8.1</v>
       </c>
       <c r="D687" t="n">
-        <v>11.82</v>
+        <v>12.81</v>
       </c>
       <c r="E687" t="n">
-        <v>9.06</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>US20825C1045</t>
+          <t>US2091151041</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>11.87</v>
+        <v>22.15</v>
       </c>
       <c r="C688" t="n">
-        <v>8.1</v>
+        <v>20.43</v>
       </c>
       <c r="D688" t="n">
-        <v>12.81</v>
+        <v>12.61</v>
       </c>
       <c r="E688" t="n">
-        <v>12.7</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>US2091151041</t>
+          <t>US21036P1084</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="C689" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="D689" t="n">
-        <v>12.61</v>
-      </c>
+        <v>23.24</v>
+      </c>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="inlineStr"/>
       <c r="E689" t="n">
-        <v>17.03</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>US21036P1084</t>
+          <t>US2193501051</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
+        <v>29.12</v>
+      </c>
+      <c r="C690" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D690" t="n">
+        <v>45.02</v>
+      </c>
       <c r="E690" t="n">
-        <v>26.47</v>
+        <v>81.61</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>US2193501051</t>
+          <t>US22052L1044</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>29.12</v>
+        <v>19.93</v>
       </c>
       <c r="C691" t="n">
-        <v>20.8</v>
+        <v>37.13</v>
       </c>
       <c r="D691" t="n">
-        <v>45.02</v>
+        <v>46.42</v>
       </c>
       <c r="E691" t="n">
-        <v>81.61</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>US22052L1044</t>
+          <t>US22160K1051</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>19.93</v>
+        <v>39.97</v>
       </c>
       <c r="C692" t="n">
-        <v>37.13</v>
+        <v>40.47</v>
       </c>
       <c r="D692" t="n">
-        <v>46.42</v>
+        <v>38.44</v>
       </c>
       <c r="E692" t="n">
-        <v>43.71</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>US22160K1051</t>
+          <t>US2310211063</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>39.97</v>
+        <v>14.94</v>
       </c>
       <c r="C693" t="n">
-        <v>40.47</v>
+        <v>16.03</v>
       </c>
       <c r="D693" t="n">
-        <v>38.44</v>
+        <v>46.51</v>
       </c>
       <c r="E693" t="n">
-        <v>53.87</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>US2310211063</t>
+          <t>US2358511028</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>14.94</v>
+        <v>38.19</v>
       </c>
       <c r="C694" t="n">
-        <v>16.03</v>
+        <v>27.47</v>
       </c>
       <c r="D694" t="n">
-        <v>46.51</v>
+        <v>36.24</v>
       </c>
       <c r="E694" t="n">
-        <v>12.29</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>US2358511028</t>
+          <t>US2371941053</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>38.19</v>
+        <v>30</v>
       </c>
       <c r="C695" t="n">
-        <v>27.47</v>
+        <v>17.06</v>
       </c>
       <c r="D695" t="n">
-        <v>36.24</v>
+        <v>20.19</v>
       </c>
       <c r="E695" t="n">
-        <v>43.4</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>US2371941053</t>
-        </is>
-      </c>
-      <c r="B696" t="n">
-        <v>30</v>
-      </c>
-      <c r="C696" t="n">
-        <v>17.06</v>
-      </c>
+          <t>US23804L1035</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr"/>
+      <c r="C696" t="inlineStr"/>
       <c r="D696" t="n">
-        <v>20.19</v>
+        <v>875.76</v>
       </c>
       <c r="E696" t="n">
-        <v>17.35</v>
+        <v>278.86</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>US23804L1035</t>
-        </is>
-      </c>
-      <c r="B697" t="inlineStr"/>
-      <c r="C697" t="inlineStr"/>
+          <t>US2435371073</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="C697" t="n">
+        <v>16.83</v>
+      </c>
       <c r="D697" t="n">
-        <v>875.76</v>
+        <v>23.21</v>
       </c>
       <c r="E697" t="n">
-        <v>278.86</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>US2435371073</t>
+          <t>US2441991054</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>24.53</v>
+        <v>18.03</v>
       </c>
       <c r="C698" t="n">
-        <v>16.83</v>
+        <v>17.05</v>
       </c>
       <c r="D698" t="n">
-        <v>23.21</v>
+        <v>10.43</v>
       </c>
       <c r="E698" t="n">
-        <v>32.28</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>US2441991054</t>
+          <t>US24703L2025</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>18.03</v>
+        <v>17.27</v>
       </c>
       <c r="C699" t="n">
-        <v>17.05</v>
+        <v>8.01</v>
       </c>
       <c r="D699" t="n">
-        <v>10.43</v>
+        <v>13.02</v>
       </c>
       <c r="E699" t="n">
-        <v>15.92</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>US24703L2025</t>
+          <t>US2473617023</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>17.27</v>
+        <v>89.47</v>
       </c>
       <c r="C700" t="n">
-        <v>8.01</v>
+        <v>15.98</v>
       </c>
       <c r="D700" t="n">
-        <v>13.02</v>
+        <v>5.61</v>
       </c>
       <c r="E700" t="n">
-        <v>19.79</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>US2473617023</t>
+          <t>US25179M1036</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>89.47</v>
+        <v>10.53</v>
       </c>
       <c r="C701" t="n">
-        <v>15.98</v>
+        <v>6.74</v>
       </c>
       <c r="D701" t="n">
-        <v>5.61</v>
+        <v>7.76</v>
       </c>
       <c r="E701" t="n">
-        <v>11.34</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>US25179M1036</t>
+          <t>US2521311074</t>
         </is>
       </c>
       <c r="B702" t="n">
-        <v>10.53</v>
+        <v>347.41</v>
       </c>
       <c r="C702" t="n">
-        <v>6.74</v>
+        <v>141.89</v>
       </c>
       <c r="D702" t="n">
-        <v>7.76</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E702" t="n">
-        <v>7.18</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>US2521311074</t>
+          <t>US25278X1090</t>
         </is>
       </c>
       <c r="B703" t="n">
-        <v>347.41</v>
+        <v>8.77</v>
       </c>
       <c r="C703" t="n">
-        <v>141.89</v>
+        <v>5.56</v>
       </c>
       <c r="D703" t="n">
-        <v>95.29000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="E703" t="n">
-        <v>54.61</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>US25278X1090</t>
+          <t>US2533931026</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>8.77</v>
+        <v>11.71</v>
       </c>
       <c r="C704" t="n">
-        <v>5.56</v>
+        <v>8.16</v>
       </c>
       <c r="D704" t="n">
-        <v>8.94</v>
+        <v>11.71</v>
       </c>
       <c r="E704" t="n">
-        <v>10.55</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>US2533931026</t>
+          <t>US2546871060</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>11.71</v>
+        <v>161.27</v>
       </c>
       <c r="C705" t="n">
-        <v>8.16</v>
+        <v>54.8</v>
       </c>
       <c r="D705" t="n">
-        <v>11.71</v>
+        <v>63.01</v>
       </c>
       <c r="E705" t="n">
-        <v>12.81</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>US2546871060</t>
+          <t>US2566771059</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>161.27</v>
+        <v>18.33</v>
       </c>
       <c r="C706" t="n">
-        <v>54.8</v>
+        <v>20.08</v>
       </c>
       <c r="D706" t="n">
-        <v>63.01</v>
+        <v>21.36</v>
       </c>
       <c r="E706" t="n">
-        <v>35.36</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>US2566771059</t>
+          <t>US2567461080</t>
         </is>
       </c>
       <c r="B707" t="n">
-        <v>18.33</v>
+        <v>17.98</v>
       </c>
       <c r="C707" t="n">
-        <v>20.08</v>
+        <v>22.16</v>
       </c>
       <c r="D707" t="n">
-        <v>21.36</v>
-      </c>
-      <c r="E707" t="n">
-        <v>18.03</v>
-      </c>
+        <v>20.86</v>
+      </c>
+      <c r="E707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>US2567461080</t>
+          <t>US25746U1097</t>
         </is>
       </c>
       <c r="B708" t="n">
-        <v>17.98</v>
+        <v>19.73</v>
       </c>
       <c r="C708" t="n">
-        <v>22.16</v>
+        <v>56.13</v>
       </c>
       <c r="D708" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="E708" t="inlineStr"/>
+        <v>20.55</v>
+      </c>
+      <c r="E708" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>US25746U1097</t>
+          <t>US2605571031</t>
         </is>
       </c>
       <c r="B709" t="n">
-        <v>19.73</v>
+        <v>6.77</v>
       </c>
       <c r="C709" t="n">
-        <v>56.13</v>
+        <v>8.02</v>
       </c>
       <c r="D709" t="n">
-        <v>20.55</v>
+        <v>67.27</v>
       </c>
       <c r="E709" t="n">
-        <v>22.1</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>US2605571031</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="B710" t="n">
-        <v>6.77</v>
+        <v>21.22</v>
       </c>
       <c r="C710" t="n">
-        <v>8.02</v>
+        <v>32.45</v>
       </c>
       <c r="D710" t="n">
-        <v>67.27</v>
+        <v>17.86</v>
       </c>
       <c r="E710" t="n">
-        <v>25.63</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US26875P1012</t>
         </is>
       </c>
       <c r="B711" t="n">
-        <v>21.22</v>
+        <v>11.12</v>
       </c>
       <c r="C711" t="n">
-        <v>32.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D711" t="n">
-        <v>17.86</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E711" t="n">
-        <v>18.96</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>US26875P1012</t>
-        </is>
-      </c>
-      <c r="B712" t="n">
-        <v>11.12</v>
-      </c>
+          <t>US26884L1098</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr"/>
       <c r="C712" t="n">
-        <v>9.800000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="D712" t="n">
-        <v>9.300000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="E712" t="n">
-        <v>10.89</v>
+        <v>102.88</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>US26884L1098</t>
+          <t>US2786421030</t>
         </is>
       </c>
       <c r="B713" t="inlineStr"/>
-      <c r="C713" t="n">
-        <v>7.73</v>
-      </c>
+      <c r="C713" t="inlineStr"/>
       <c r="D713" t="n">
-        <v>9.17</v>
+        <v>8.4</v>
       </c>
       <c r="E713" t="n">
-        <v>102.88</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>US2786421030</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr"/>
-      <c r="C714" t="inlineStr"/>
-      <c r="D714" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="E714" t="n">
-        <v>15.71</v>
-      </c>
+          <t>US2787681061</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="C714" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>US2787681061</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="B715" t="n">
-        <v>32.52</v>
+        <v>60.02</v>
       </c>
       <c r="C715" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr"/>
+        <v>38.21</v>
+      </c>
+      <c r="D715" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="E715" t="n">
+        <v>31.79</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US28176E1082</t>
         </is>
       </c>
       <c r="B716" t="n">
-        <v>60.02</v>
+        <v>54.4</v>
       </c>
       <c r="C716" t="n">
-        <v>38.21</v>
+        <v>30.6</v>
       </c>
       <c r="D716" t="n">
-        <v>41.41</v>
+        <v>33.13</v>
       </c>
       <c r="E716" t="n">
-        <v>31.79</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>US28176E1082</t>
-        </is>
-      </c>
-      <c r="B717" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="C717" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="D717" t="n">
-        <v>33.13</v>
-      </c>
+          <t>US28414H1032</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr"/>
+      <c r="C717" t="inlineStr"/>
+      <c r="D717" t="inlineStr"/>
       <c r="E717" t="n">
-        <v>50.73</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>US28414H1032</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr"/>
-      <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
+          <t>US2855121099</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="C718" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="D718" t="n">
+        <v>41.75</v>
+      </c>
       <c r="E718" t="n">
-        <v>17.82</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>US2855121099</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="B719" t="n">
-        <v>47.23</v>
+        <v>24.62</v>
       </c>
       <c r="C719" t="n">
-        <v>45.86</v>
+        <v>13.51</v>
       </c>
       <c r="D719" t="n">
-        <v>41.75</v>
+        <v>25.91</v>
       </c>
       <c r="E719" t="n">
-        <v>28.35</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US29355A1079</t>
         </is>
       </c>
       <c r="B720" t="n">
-        <v>24.62</v>
+        <v>179.49</v>
       </c>
       <c r="C720" t="n">
-        <v>13.51</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D720" t="n">
-        <v>25.91</v>
+        <v>42.89</v>
       </c>
       <c r="E720" t="n">
-        <v>31.9</v>
+        <v>91.45</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>US29355A1079</t>
+          <t>US29364G1031</t>
         </is>
       </c>
       <c r="B721" t="n">
-        <v>179.49</v>
+        <v>20.33</v>
       </c>
       <c r="C721" t="n">
-        <v>95.65000000000001</v>
+        <v>20.96</v>
       </c>
       <c r="D721" t="n">
-        <v>42.89</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E721" t="n">
-        <v>91.45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>US29364G1031</t>
+          <t>US2944291051</t>
         </is>
       </c>
       <c r="B722" t="n">
-        <v>20.33</v>
+        <v>48.63</v>
       </c>
       <c r="C722" t="n">
-        <v>20.96</v>
+        <v>34.42</v>
       </c>
       <c r="D722" t="n">
-        <v>9.119999999999999</v>
+        <v>56.19</v>
       </c>
       <c r="E722" t="n">
-        <v>31</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>US2944291051</t>
-        </is>
-      </c>
-      <c r="B723" t="n">
-        <v>48.63</v>
-      </c>
+          <t>US29452E1010</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr"/>
       <c r="C723" t="n">
-        <v>34.42</v>
+        <v>6.39</v>
       </c>
       <c r="D723" t="n">
-        <v>56.19</v>
+        <v>9.58</v>
       </c>
       <c r="E723" t="n">
-        <v>52.69</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>US29452E1010</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr"/>
-      <c r="C724" t="n">
-        <v>6.39</v>
-      </c>
+          <t>US29786A1060</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="C724" t="inlineStr"/>
       <c r="D724" t="n">
-        <v>9.58</v>
+        <v>36.19</v>
       </c>
       <c r="E724" t="n">
-        <v>12.49</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>US29786A1060</t>
+          <t>US30161N1019</t>
         </is>
       </c>
       <c r="B725" t="n">
-        <v>64.44</v>
-      </c>
-      <c r="C725" t="inlineStr"/>
+        <v>33.18</v>
+      </c>
+      <c r="C725" t="n">
+        <v>19.66</v>
+      </c>
       <c r="D725" t="n">
-        <v>36.19</v>
+        <v>15.37</v>
       </c>
       <c r="E725" t="n">
-        <v>22.5</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>US30161N1019</t>
-        </is>
-      </c>
-      <c r="B726" t="n">
-        <v>33.18</v>
-      </c>
+          <t>US30212P3038</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr"/>
       <c r="C726" t="n">
-        <v>19.66</v>
+        <v>40.25</v>
       </c>
       <c r="D726" t="n">
-        <v>15.37</v>
+        <v>28.61</v>
       </c>
       <c r="E726" t="n">
-        <v>15.35</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>US30212P3038</t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr"/>
+          <t>US30231G1022</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>11.35</v>
+      </c>
       <c r="C727" t="n">
-        <v>40.25</v>
+        <v>8.32</v>
       </c>
       <c r="D727" t="n">
-        <v>28.61</v>
+        <v>11.25</v>
       </c>
       <c r="E727" t="n">
-        <v>20.83</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>US30231G1022</t>
+          <t>US30303M1027</t>
         </is>
       </c>
       <c r="B728" t="n">
-        <v>11.35</v>
+        <v>24.43</v>
       </c>
       <c r="C728" t="n">
-        <v>8.32</v>
+        <v>14.02</v>
       </c>
       <c r="D728" t="n">
-        <v>11.25</v>
+        <v>23.8</v>
       </c>
       <c r="E728" t="n">
-        <v>13.73</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>US30303M1027</t>
+          <t>US3119001044</t>
         </is>
       </c>
       <c r="B729" t="n">
-        <v>24.43</v>
+        <v>39.97</v>
       </c>
       <c r="C729" t="n">
-        <v>14.02</v>
+        <v>25.06</v>
       </c>
       <c r="D729" t="n">
-        <v>23.8</v>
+        <v>32.13</v>
       </c>
       <c r="E729" t="n">
-        <v>24.54</v>
+        <v>35.89</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>US3119001044</t>
+          <t>US31428X1063</t>
         </is>
       </c>
       <c r="B730" t="n">
-        <v>39.97</v>
+        <v>16.16</v>
       </c>
       <c r="C730" t="n">
-        <v>25.06</v>
+        <v>15.64</v>
       </c>
       <c r="D730" t="n">
-        <v>32.13</v>
+        <v>14.07</v>
       </c>
       <c r="E730" t="n">
-        <v>35.89</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>US31428X1063</t>
+          <t>US31488V1070</t>
         </is>
       </c>
       <c r="B731" t="n">
-        <v>16.16</v>
+        <v>16.79</v>
       </c>
       <c r="C731" t="n">
-        <v>15.64</v>
+        <v>12.93</v>
       </c>
       <c r="D731" t="n">
-        <v>14.07</v>
+        <v>17.73</v>
       </c>
       <c r="E731" t="n">
-        <v>14.74</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>US31488V1070</t>
+          <t>US31620M1062</t>
         </is>
       </c>
       <c r="B732" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="C732" t="n">
-        <v>12.93</v>
-      </c>
-      <c r="D732" t="n">
-        <v>17.73</v>
-      </c>
+        <v>162.55</v>
+      </c>
+      <c r="C732" t="inlineStr"/>
+      <c r="D732" t="inlineStr"/>
       <c r="E732" t="n">
-        <v>26.11</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>US31620M1062</t>
+          <t>US3364331070</t>
         </is>
       </c>
       <c r="B733" t="n">
-        <v>162.55</v>
+        <v>19.88</v>
       </c>
       <c r="C733" t="inlineStr"/>
-      <c r="D733" t="inlineStr"/>
+      <c r="D733" t="n">
+        <v>22.27</v>
+      </c>
       <c r="E733" t="n">
-        <v>56.96</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>US3364331070</t>
+          <t>US3377381088</t>
         </is>
       </c>
       <c r="B734" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="C734" t="inlineStr"/>
+        <v>52.25</v>
+      </c>
+      <c r="C734" t="n">
+        <v>25.88</v>
+      </c>
       <c r="D734" t="n">
-        <v>22.27</v>
+        <v>26.67</v>
       </c>
       <c r="E734" t="n">
-        <v>14.67</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>US3377381088</t>
+          <t>US3453708600</t>
         </is>
       </c>
       <c r="B735" t="n">
-        <v>52.25</v>
-      </c>
-      <c r="C735" t="n">
-        <v>25.88</v>
-      </c>
+        <v>4.67</v>
+      </c>
+      <c r="C735" t="inlineStr"/>
       <c r="D735" t="n">
-        <v>26.67</v>
+        <v>11.33</v>
       </c>
       <c r="E735" t="n">
-        <v>38.19</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>US3453708600</t>
+          <t>US34959J1088</t>
         </is>
       </c>
       <c r="B736" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="C736" t="inlineStr"/>
+        <v>46.83</v>
+      </c>
+      <c r="C736" t="n">
+        <v>30.7</v>
+      </c>
       <c r="D736" t="n">
-        <v>11.33</v>
+        <v>30.24</v>
       </c>
       <c r="E736" t="n">
-        <v>6.77</v>
+        <v>31.77</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>US34959J1088</t>
+          <t>US35137L1052</t>
         </is>
       </c>
       <c r="B737" t="n">
-        <v>46.83</v>
+        <v>10.28</v>
       </c>
       <c r="C737" t="n">
-        <v>30.7</v>
+        <v>15.21</v>
       </c>
       <c r="D737" t="n">
-        <v>30.24</v>
+        <v>14.57</v>
       </c>
       <c r="E737" t="n">
-        <v>31.77</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>US35137L1052</t>
+          <t>US35671D8570</t>
         </is>
       </c>
       <c r="B738" t="n">
-        <v>10.28</v>
+        <v>14.39</v>
       </c>
       <c r="C738" t="n">
-        <v>15.21</v>
+        <v>15.93</v>
       </c>
       <c r="D738" t="n">
-        <v>14.57</v>
+        <v>33.35</v>
       </c>
       <c r="E738" t="n">
-        <v>10.99</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>US35671D8570</t>
-        </is>
-      </c>
-      <c r="B739" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="C739" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="D739" t="n">
-        <v>33.35</v>
-      </c>
+          <t>US36467W1099</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr"/>
+      <c r="C739" t="inlineStr"/>
+      <c r="D739" t="inlineStr"/>
       <c r="E739" t="n">
-        <v>29.22</v>
+        <v>669.55</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>US36467W1099</t>
+          <t>US3647601083</t>
         </is>
       </c>
       <c r="B740" t="inlineStr"/>
-      <c r="C740" t="inlineStr"/>
+      <c r="C740" t="n">
+        <v>26.59</v>
+      </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="n">
-        <v>669.55</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>US3647601083</t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr"/>
+          <t>US3695501086</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>18.05</v>
+      </c>
       <c r="C741" t="n">
-        <v>26.59</v>
-      </c>
-      <c r="D741" t="inlineStr"/>
+        <v>20.36</v>
+      </c>
+      <c r="D741" t="n">
+        <v>21.6</v>
+      </c>
       <c r="E741" t="n">
-        <v>14.84</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>US3695501086</t>
-        </is>
-      </c>
-      <c r="B742" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="C742" t="n">
-        <v>20.36</v>
-      </c>
+          <t>US3696043013</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr"/>
+      <c r="C742" t="inlineStr"/>
       <c r="D742" t="n">
-        <v>21.6</v>
+        <v>15.29</v>
       </c>
       <c r="E742" t="n">
-        <v>19.33</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>US3696043013</t>
-        </is>
-      </c>
-      <c r="B743" t="inlineStr"/>
-      <c r="C743" t="inlineStr"/>
+          <t>US3703341046</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="C743" t="n">
+        <v>15.81</v>
+      </c>
       <c r="D743" t="n">
-        <v>15.29</v>
+        <v>19.51</v>
       </c>
       <c r="E743" t="n">
-        <v>27.91</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>US3703341046</t>
+          <t>US37045V1008</t>
         </is>
       </c>
       <c r="B744" t="n">
-        <v>16.63</v>
+        <v>8.75</v>
       </c>
       <c r="C744" t="n">
-        <v>15.81</v>
+        <v>5.49</v>
       </c>
       <c r="D744" t="n">
-        <v>19.51</v>
+        <v>4.91</v>
       </c>
       <c r="E744" t="n">
-        <v>15.85</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>US37045V1008</t>
+          <t>US3755581036</t>
         </is>
       </c>
       <c r="B745" t="n">
-        <v>8.75</v>
+        <v>14.72</v>
       </c>
       <c r="C745" t="n">
-        <v>5.49</v>
+        <v>23.59</v>
       </c>
       <c r="D745" t="n">
-        <v>4.91</v>
+        <v>17.99</v>
       </c>
       <c r="E745" t="n">
-        <v>8.369999999999999</v>
+        <v>241.49</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>US3755581036</t>
+          <t>US37940X1028</t>
         </is>
       </c>
       <c r="B746" t="n">
-        <v>14.72</v>
+        <v>41.12</v>
       </c>
       <c r="C746" t="n">
-        <v>23.59</v>
+        <v>245.48</v>
       </c>
       <c r="D746" t="n">
-        <v>17.99</v>
+        <v>33.7</v>
       </c>
       <c r="E746" t="n">
-        <v>241.49</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>US37940X1028</t>
+          <t>US38141G1040</t>
         </is>
       </c>
       <c r="B747" t="n">
-        <v>41.12</v>
+        <v>6.44</v>
       </c>
       <c r="C747" t="n">
-        <v>245.48</v>
+        <v>11.42</v>
       </c>
       <c r="D747" t="n">
-        <v>33.7</v>
+        <v>16.87</v>
       </c>
       <c r="E747" t="n">
-        <v>18.19</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>US38141G1040</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="B748" t="n">
-        <v>6.44</v>
+        <v>25.94</v>
       </c>
       <c r="C748" t="n">
-        <v>11.42</v>
+        <v>18.37</v>
       </c>
       <c r="D748" t="n">
-        <v>16.87</v>
+        <v>22.7</v>
       </c>
       <c r="E748" t="n">
-        <v>14.12</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US40434L1052</t>
         </is>
       </c>
       <c r="B749" t="n">
-        <v>25.94</v>
+        <v>5.69</v>
       </c>
       <c r="C749" t="n">
-        <v>18.37</v>
+        <v>9.26</v>
       </c>
       <c r="D749" t="n">
-        <v>22.7</v>
+        <v>8.07</v>
       </c>
       <c r="E749" t="n">
-        <v>27.06</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>US40434L1052</t>
+          <t>US4062161017</t>
         </is>
       </c>
       <c r="B750" t="n">
-        <v>5.69</v>
+        <v>14</v>
       </c>
       <c r="C750" t="n">
-        <v>9.26</v>
+        <v>22.73</v>
       </c>
       <c r="D750" t="n">
-        <v>8.07</v>
+        <v>12.36</v>
       </c>
       <c r="E750" t="n">
-        <v>12.66</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>US4062161017</t>
+          <t>US4165151048</t>
         </is>
       </c>
       <c r="B751" t="n">
-        <v>14</v>
+        <v>10.43</v>
       </c>
       <c r="C751" t="n">
-        <v>22.73</v>
+        <v>13.93</v>
       </c>
       <c r="D751" t="n">
-        <v>12.36</v>
+        <v>10.08</v>
       </c>
       <c r="E751" t="n">
-        <v>9.6</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>US4165151048</t>
+          <t>US4227041062</t>
         </is>
       </c>
       <c r="B752" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="C752" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="D752" t="n">
-        <v>10.08</v>
-      </c>
+        <v>81.06</v>
+      </c>
+      <c r="C752" t="inlineStr"/>
+      <c r="D752" t="inlineStr"/>
       <c r="E752" t="n">
-        <v>10.57</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>US4227041062</t>
+          <t>US4278661081</t>
         </is>
       </c>
       <c r="B753" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="C753" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="D753" t="n">
+        <v>20.58</v>
+      </c>
       <c r="E753" t="n">
-        <v>86.75</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>US4278661081</t>
+          <t>US42824C1099</t>
         </is>
       </c>
       <c r="B754" t="n">
-        <v>27.2</v>
+        <v>5.69</v>
       </c>
       <c r="C754" t="n">
-        <v>29.08</v>
+        <v>21.73</v>
       </c>
       <c r="D754" t="n">
-        <v>20.58</v>
+        <v>9.99</v>
       </c>
       <c r="E754" t="n">
-        <v>15.51</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>US42824C1099</t>
+          <t>US43300A2033</t>
         </is>
       </c>
       <c r="B755" t="n">
-        <v>5.69</v>
+        <v>106.15</v>
       </c>
       <c r="C755" t="n">
-        <v>21.73</v>
+        <v>27.89</v>
       </c>
       <c r="D755" t="n">
-        <v>9.99</v>
+        <v>42.13</v>
       </c>
       <c r="E755" t="n">
-        <v>10.2</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>US43300A2033</t>
+          <t>US4370761029</t>
         </is>
       </c>
       <c r="B756" t="n">
-        <v>106.15</v>
+        <v>22.69</v>
       </c>
       <c r="C756" t="n">
-        <v>27.89</v>
+        <v>23.6</v>
       </c>
       <c r="D756" t="n">
-        <v>42.13</v>
+        <v>18.98</v>
       </c>
       <c r="E756" t="n">
-        <v>40.25</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>US4370761029</t>
+          <t>US4385161066</t>
         </is>
       </c>
       <c r="B757" t="n">
-        <v>22.69</v>
+        <v>26.35</v>
       </c>
       <c r="C757" t="n">
-        <v>23.6</v>
+        <v>29.48</v>
       </c>
       <c r="D757" t="n">
-        <v>18.98</v>
+        <v>24.77</v>
       </c>
       <c r="E757" t="n">
-        <v>23.51</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>US4385161066</t>
+          <t>US4432011082</t>
         </is>
       </c>
       <c r="B758" t="n">
-        <v>26.35</v>
+        <v>54.09</v>
       </c>
       <c r="C758" t="n">
-        <v>29.48</v>
+        <v>35.53</v>
       </c>
       <c r="D758" t="n">
-        <v>24.77</v>
+        <v>29.51</v>
       </c>
       <c r="E758" t="n">
-        <v>25.95</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>US4432011082</t>
-        </is>
-      </c>
-      <c r="B759" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="C759" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="D759" t="n">
-        <v>29.51</v>
-      </c>
+          <t>US4435731009</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr"/>
+      <c r="C759" t="inlineStr"/>
+      <c r="D759" t="inlineStr"/>
       <c r="E759" t="n">
-        <v>38.89</v>
+        <v>7802.58</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>US4435731009</t>
-        </is>
-      </c>
-      <c r="B760" t="inlineStr"/>
-      <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr"/>
+          <t>US4461501045</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="C760" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D760" t="n">
+        <v>10.28</v>
+      </c>
       <c r="E760" t="n">
-        <v>7802.58</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>US4461501045</t>
+          <t>US45168D1046</t>
         </is>
       </c>
       <c r="B761" t="n">
-        <v>17.21</v>
+        <v>76.53</v>
       </c>
       <c r="C761" t="n">
-        <v>9.720000000000001</v>
+        <v>50.82</v>
       </c>
       <c r="D761" t="n">
-        <v>10.28</v>
+        <v>55.16</v>
       </c>
       <c r="E761" t="n">
-        <v>13.34</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>US45168D1046</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="B762" t="n">
-        <v>76.53</v>
+        <v>28.99</v>
       </c>
       <c r="C762" t="n">
-        <v>50.82</v>
+        <v>22.56</v>
       </c>
       <c r="D762" t="n">
-        <v>55.16</v>
+        <v>26.89</v>
       </c>
       <c r="E762" t="n">
-        <v>38.76</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US4523271090</t>
         </is>
       </c>
       <c r="B763" t="n">
-        <v>28.99</v>
-      </c>
-      <c r="C763" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="D763" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="E763" t="n">
-        <v>21.65</v>
-      </c>
+        <v>75.39</v>
+      </c>
+      <c r="C763" t="inlineStr"/>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>US4523271090</t>
+          <t>US4581401001</t>
         </is>
       </c>
       <c r="B764" t="n">
-        <v>75.39</v>
-      </c>
-      <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
+        <v>10.56</v>
+      </c>
+      <c r="C764" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="D764" t="n">
+        <v>125.31</v>
+      </c>
       <c r="E764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>US4581401001</t>
+          <t>US45866F1049</t>
         </is>
       </c>
       <c r="B765" t="n">
-        <v>10.56</v>
+        <v>19.04</v>
       </c>
       <c r="C765" t="n">
-        <v>13.59</v>
+        <v>39.8</v>
       </c>
       <c r="D765" t="n">
-        <v>125.31</v>
-      </c>
-      <c r="E765" t="inlineStr"/>
+        <v>30.64</v>
+      </c>
+      <c r="E765" t="n">
+        <v>31.17</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>US45866F1049</t>
+          <t>US4592001014</t>
         </is>
       </c>
       <c r="B766" t="n">
-        <v>19.04</v>
+        <v>21.05</v>
       </c>
       <c r="C766" t="n">
-        <v>39.8</v>
+        <v>78.42</v>
       </c>
       <c r="D766" t="n">
-        <v>30.64</v>
+        <v>20.1</v>
       </c>
       <c r="E766" t="n">
-        <v>31.17</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>US4592001014</t>
+          <t>US4612021034</t>
         </is>
       </c>
       <c r="B767" t="n">
-        <v>21.05</v>
+        <v>70.17</v>
       </c>
       <c r="C767" t="n">
-        <v>78.42</v>
+        <v>62.71</v>
       </c>
       <c r="D767" t="n">
-        <v>20.1</v>
+        <v>60.74</v>
       </c>
       <c r="E767" t="n">
-        <v>34.2</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>US4612021034</t>
+          <t>US46120E6023</t>
         </is>
       </c>
       <c r="B768" t="n">
-        <v>70.17</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C768" t="n">
-        <v>62.71</v>
+        <v>72.64</v>
       </c>
       <c r="D768" t="n">
-        <v>60.74</v>
+        <v>67.06</v>
       </c>
       <c r="E768" t="n">
-        <v>62.05</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>US46120E6023</t>
+          <t>US46266C1053</t>
         </is>
       </c>
       <c r="B769" t="n">
-        <v>77.09999999999999</v>
+        <v>56.95</v>
       </c>
       <c r="C769" t="n">
-        <v>72.64</v>
+        <v>35.79</v>
       </c>
       <c r="D769" t="n">
-        <v>67.06</v>
+        <v>31.74</v>
       </c>
       <c r="E769" t="n">
-        <v>81.34999999999999</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>US46266C1053</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="B770" t="n">
-        <v>56.95</v>
+        <v>10.31</v>
       </c>
       <c r="C770" t="n">
-        <v>35.79</v>
+        <v>11.1</v>
       </c>
       <c r="D770" t="n">
-        <v>31.74</v>
+        <v>10.48</v>
       </c>
       <c r="E770" t="n">
-        <v>26.25</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="B771" t="n">
-        <v>10.31</v>
+        <v>21.91</v>
       </c>
       <c r="C771" t="n">
-        <v>11.1</v>
+        <v>26.23</v>
       </c>
       <c r="D771" t="n">
-        <v>10.48</v>
+        <v>28.32</v>
       </c>
       <c r="E771" t="n">
-        <v>12.14</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US4824801009</t>
         </is>
       </c>
       <c r="B772" t="n">
-        <v>21.91</v>
+        <v>24.25</v>
       </c>
       <c r="C772" t="n">
-        <v>26.23</v>
+        <v>14.56</v>
       </c>
       <c r="D772" t="n">
-        <v>28.32</v>
+        <v>20.08</v>
       </c>
       <c r="E772" t="n">
-        <v>24.98</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>US4824801009</t>
+          <t>US4932671088</t>
         </is>
       </c>
       <c r="B773" t="n">
-        <v>24.25</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C773" t="n">
-        <v>14.56</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D773" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="E773" t="n">
-        <v>40.66</v>
-      </c>
+        <v>16.3</v>
+      </c>
+      <c r="E773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>US4932671088</t>
+          <t>US49338L1035</t>
         </is>
       </c>
       <c r="B774" t="n">
-        <v>8.789999999999999</v>
+        <v>37.65</v>
       </c>
       <c r="C774" t="n">
-        <v>9.029999999999999</v>
+        <v>28.2</v>
       </c>
       <c r="D774" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="E774" t="inlineStr"/>
+        <v>20.67</v>
+      </c>
+      <c r="E774" t="n">
+        <v>42.47</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>US49338L1035</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="B775" t="n">
-        <v>37.65</v>
+        <v>26.69</v>
       </c>
       <c r="C775" t="n">
-        <v>28.2</v>
+        <v>23.75</v>
       </c>
       <c r="D775" t="n">
-        <v>20.67</v>
+        <v>23.34</v>
       </c>
       <c r="E775" t="n">
-        <v>42.47</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US49456B1017</t>
         </is>
       </c>
       <c r="B776" t="n">
-        <v>26.69</v>
+        <v>20.3</v>
       </c>
       <c r="C776" t="n">
-        <v>23.75</v>
+        <v>16.1</v>
       </c>
       <c r="D776" t="n">
-        <v>23.34</v>
+        <v>16.58</v>
       </c>
       <c r="E776" t="n">
-        <v>17.35</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>US49456B1017</t>
+          <t>US5007541064</t>
         </is>
       </c>
       <c r="B777" t="n">
-        <v>20.3</v>
+        <v>43.05</v>
       </c>
       <c r="C777" t="n">
-        <v>16.1</v>
+        <v>21.28</v>
       </c>
       <c r="D777" t="n">
-        <v>16.58</v>
+        <v>16</v>
       </c>
       <c r="E777" t="n">
-        <v>23.41</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>US5007541064</t>
+          <t>US5010441013</t>
         </is>
       </c>
       <c r="B778" t="n">
-        <v>43.05</v>
+        <v>10.54</v>
       </c>
       <c r="C778" t="n">
-        <v>21.28</v>
+        <v>20</v>
       </c>
       <c r="D778" t="n">
-        <v>16</v>
+        <v>14.73</v>
       </c>
       <c r="E778" t="n">
-        <v>13.58</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>US5010441013</t>
+          <t>US5024311095</t>
         </is>
       </c>
       <c r="B779" t="n">
-        <v>10.54</v>
+        <v>23.47</v>
       </c>
       <c r="C779" t="n">
-        <v>20</v>
+        <v>37.94</v>
       </c>
       <c r="D779" t="n">
-        <v>14.73</v>
+        <v>32.72</v>
       </c>
       <c r="E779" t="n">
-        <v>15.59</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>US5024311095</t>
+          <t>US5128073062</t>
         </is>
       </c>
       <c r="B780" t="n">
-        <v>23.47</v>
+        <v>23.44</v>
       </c>
       <c r="C780" t="n">
-        <v>37.94</v>
+        <v>13.75</v>
       </c>
       <c r="D780" t="n">
-        <v>32.72</v>
+        <v>18.33</v>
       </c>
       <c r="E780" t="n">
-        <v>26.96</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>US5128073062</t>
-        </is>
-      </c>
-      <c r="B781" t="n">
-        <v>23.44</v>
-      </c>
-      <c r="C781" t="n">
-        <v>13.75</v>
-      </c>
+          <t>US5178341070</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr"/>
+      <c r="C781" t="inlineStr"/>
       <c r="D781" t="n">
-        <v>18.33</v>
+        <v>30.83</v>
       </c>
       <c r="E781" t="n">
-        <v>36.72</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>US5178341070</t>
-        </is>
-      </c>
-      <c r="B782" t="inlineStr"/>
-      <c r="C782" t="inlineStr"/>
+          <t>US5184391044</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="C782" t="n">
+        <v>38.88</v>
+      </c>
       <c r="D782" t="n">
-        <v>30.83</v>
+        <v>70.45</v>
       </c>
       <c r="E782" t="n">
-        <v>26.18</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>US5184391044</t>
+          <t>US5261071071</t>
         </is>
       </c>
       <c r="B783" t="n">
-        <v>40.81</v>
+        <v>26.21</v>
       </c>
       <c r="C783" t="n">
-        <v>38.88</v>
+        <v>17.23</v>
       </c>
       <c r="D783" t="n">
-        <v>70.45</v>
+        <v>27.07</v>
       </c>
       <c r="E783" t="n">
-        <v>98.44</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>US5261071071</t>
+          <t>US5324571083</t>
         </is>
       </c>
       <c r="B784" t="n">
-        <v>26.21</v>
+        <v>45.12</v>
       </c>
       <c r="C784" t="n">
-        <v>17.23</v>
+        <v>53</v>
       </c>
       <c r="D784" t="n">
-        <v>27.07</v>
+        <v>100.48</v>
       </c>
       <c r="E784" t="n">
-        <v>27.03</v>
+        <v>65.91</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>US5324571083</t>
-        </is>
-      </c>
-      <c r="B785" t="n">
-        <v>45.12</v>
-      </c>
+          <t>US5380341090</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr"/>
       <c r="C785" t="n">
-        <v>53</v>
+        <v>108.22</v>
       </c>
       <c r="D785" t="n">
-        <v>100.48</v>
+        <v>68.45</v>
       </c>
       <c r="E785" t="n">
-        <v>65.91</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>US5380341090</t>
-        </is>
-      </c>
-      <c r="B786" t="inlineStr"/>
+          <t>US5398301094</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>15.61</v>
+      </c>
       <c r="C786" t="n">
-        <v>108.22</v>
+        <v>22.46</v>
       </c>
       <c r="D786" t="n">
-        <v>68.45</v>
+        <v>16.45</v>
       </c>
       <c r="E786" t="n">
-        <v>47.28</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>US5398301094</t>
+          <t>US5500211090</t>
         </is>
       </c>
       <c r="B787" t="n">
-        <v>15.61</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="C787" t="n">
-        <v>22.46</v>
+        <v>42.2</v>
       </c>
       <c r="D787" t="n">
-        <v>16.45</v>
+        <v>46.55</v>
       </c>
       <c r="E787" t="n">
-        <v>21.78</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>US5500211090</t>
+          <t>US55024U1097</t>
         </is>
       </c>
       <c r="B788" t="n">
-        <v>73.04000000000001</v>
+        <v>16.47</v>
       </c>
       <c r="C788" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D788" t="n">
-        <v>46.55</v>
-      </c>
-      <c r="E788" t="n">
-        <v>39.18</v>
-      </c>
+        <v>29.03</v>
+      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>US55024U1097</t>
-        </is>
-      </c>
-      <c r="B789" t="n">
-        <v>16.47</v>
-      </c>
-      <c r="C789" t="n">
-        <v>29.03</v>
-      </c>
+          <t>US55087P1049</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr"/>
+      <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr"/>
-      <c r="E789" t="inlineStr"/>
+      <c r="E789" t="n">
+        <v>234.12</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>US55087P1049</t>
-        </is>
-      </c>
-      <c r="B790" t="inlineStr"/>
-      <c r="C790" t="inlineStr"/>
-      <c r="D790" t="inlineStr"/>
+          <t>US55354G1004</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="C790" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="D790" t="n">
+        <v>39.32</v>
+      </c>
       <c r="E790" t="n">
-        <v>234.12</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>US55354G1004</t>
-        </is>
-      </c>
-      <c r="B791" t="n">
-        <v>70.45</v>
-      </c>
-      <c r="C791" t="n">
-        <v>43.4</v>
-      </c>
+          <t>US5657881067</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr"/>
+      <c r="C791" t="inlineStr"/>
       <c r="D791" t="n">
-        <v>39.32</v>
+        <v>17.44</v>
       </c>
       <c r="E791" t="n">
-        <v>42.72</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>US5657881067</t>
-        </is>
-      </c>
-      <c r="B792" t="inlineStr"/>
-      <c r="C792" t="inlineStr"/>
+          <t>US56585A1025</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="C792" t="n">
+        <v>4.14</v>
+      </c>
       <c r="D792" t="n">
-        <v>17.44</v>
+        <v>6.27</v>
       </c>
       <c r="E792" t="n">
-        <v>9.66</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>US56585A1025</t>
+          <t>US5717481023</t>
         </is>
       </c>
       <c r="B793" t="n">
-        <v>23.79</v>
+        <v>28.37</v>
       </c>
       <c r="C793" t="n">
-        <v>4.14</v>
+        <v>27.4</v>
       </c>
       <c r="D793" t="n">
-        <v>6.27</v>
+        <v>25.17</v>
       </c>
       <c r="E793" t="n">
-        <v>13.82</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>US5717481023</t>
+          <t>US5719032022</t>
         </is>
       </c>
       <c r="B794" t="n">
-        <v>28.37</v>
+        <v>49.51</v>
       </c>
       <c r="C794" t="n">
-        <v>27.4</v>
+        <v>20.57</v>
       </c>
       <c r="D794" t="n">
-        <v>25.17</v>
+        <v>22.16</v>
       </c>
       <c r="E794" t="n">
-        <v>25.95</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>US5719032022</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="B795" t="n">
-        <v>49.51</v>
+        <v>41.03</v>
       </c>
       <c r="C795" t="n">
-        <v>20.57</v>
+        <v>34</v>
       </c>
       <c r="D795" t="n">
-        <v>22.16</v>
+        <v>36.04</v>
       </c>
       <c r="E795" t="n">
-        <v>33.5</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US57667L1070</t>
         </is>
       </c>
       <c r="B796" t="n">
-        <v>41.03</v>
+        <v>142.54</v>
       </c>
       <c r="C796" t="n">
-        <v>34</v>
+        <v>33.48</v>
       </c>
       <c r="D796" t="n">
-        <v>36.04</v>
+        <v>16.12</v>
       </c>
       <c r="E796" t="n">
-        <v>37.92</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>US57667L1070</t>
+          <t>US5801351017</t>
         </is>
       </c>
       <c r="B797" t="n">
-        <v>142.54</v>
+        <v>26.71</v>
       </c>
       <c r="C797" t="n">
-        <v>33.48</v>
+        <v>31.62</v>
       </c>
       <c r="D797" t="n">
-        <v>16.12</v>
+        <v>25.64</v>
       </c>
       <c r="E797" t="n">
-        <v>16.19</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>US5801351017</t>
+          <t>US58733R1023</t>
         </is>
       </c>
       <c r="B798" t="n">
-        <v>26.71</v>
+        <v>806.12</v>
       </c>
       <c r="C798" t="n">
-        <v>31.62</v>
+        <v>88.39</v>
       </c>
       <c r="D798" t="n">
-        <v>25.64</v>
+        <v>80.03</v>
       </c>
       <c r="E798" t="n">
-        <v>25.45</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>US58733R1023</t>
+          <t>US58933Y1055</t>
         </is>
       </c>
       <c r="B799" t="n">
-        <v>806.12</v>
+        <v>14.91</v>
       </c>
       <c r="C799" t="n">
-        <v>88.39</v>
+        <v>19.43</v>
       </c>
       <c r="D799" t="n">
-        <v>80.03</v>
+        <v>760.78</v>
       </c>
       <c r="E799" t="n">
-        <v>45.11</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>US58933Y1055</t>
+          <t>US59156R1086</t>
         </is>
       </c>
       <c r="B800" t="n">
-        <v>14.91</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="C800" t="n">
-        <v>19.43</v>
+        <v>24.87</v>
       </c>
       <c r="D800" t="n">
-        <v>760.78</v>
+        <v>36.53</v>
       </c>
       <c r="E800" t="n">
-        <v>14.77</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>US59156R1086</t>
+          <t>US5926881054</t>
         </is>
       </c>
       <c r="B801" t="n">
-        <v>8.550000000000001</v>
+        <v>51.77</v>
       </c>
       <c r="C801" t="n">
-        <v>24.87</v>
+        <v>37.64</v>
       </c>
       <c r="D801" t="n">
-        <v>36.53</v>
+        <v>33.79</v>
       </c>
       <c r="E801" t="n">
-        <v>13.78</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>US5926881054</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="B802" t="n">
-        <v>51.77</v>
+        <v>33.64</v>
       </c>
       <c r="C802" t="n">
-        <v>37.64</v>
+        <v>26.62</v>
       </c>
       <c r="D802" t="n">
-        <v>33.79</v>
+        <v>35.16</v>
       </c>
       <c r="E802" t="n">
-        <v>30.23</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US5950171042</t>
         </is>
       </c>
       <c r="B803" t="n">
-        <v>33.64</v>
+        <v>120.21</v>
       </c>
       <c r="C803" t="n">
-        <v>26.62</v>
+        <v>33.08</v>
       </c>
       <c r="D803" t="n">
-        <v>35.16</v>
+        <v>20.87</v>
       </c>
       <c r="E803" t="n">
-        <v>37.88</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>US5950171042</t>
+          <t>US5951121038</t>
         </is>
       </c>
       <c r="B804" t="n">
-        <v>120.21</v>
+        <v>14.4</v>
       </c>
       <c r="C804" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="D804" t="n">
-        <v>20.87</v>
-      </c>
+        <v>7.4</v>
+      </c>
+      <c r="D804" t="inlineStr"/>
       <c r="E804" t="n">
-        <v>25.78</v>
+        <v>137.33</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>US5951121038</t>
+          <t>US60770K1079</t>
         </is>
       </c>
       <c r="B805" t="n">
-        <v>14.4</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C805" t="n">
-        <v>7.4</v>
+        <v>8.94</v>
       </c>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="n">
-        <v>137.33</v>
-      </c>
+      <c r="E805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>US60770K1079</t>
+          <t>US6092071058</t>
         </is>
       </c>
       <c r="B806" t="n">
-        <v>8.970000000000001</v>
+        <v>21.79</v>
       </c>
       <c r="C806" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="D806" t="inlineStr"/>
-      <c r="E806" t="inlineStr"/>
+        <v>33.98</v>
+      </c>
+      <c r="D806" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="E806" t="n">
+        <v>17.45</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>US6092071058</t>
+          <t>US6174464486</t>
         </is>
       </c>
       <c r="B807" t="n">
-        <v>21.79</v>
+        <v>12.22</v>
       </c>
       <c r="C807" t="n">
-        <v>33.98</v>
+        <v>13.82</v>
       </c>
       <c r="D807" t="n">
-        <v>20.01</v>
+        <v>17.99</v>
       </c>
       <c r="E807" t="n">
-        <v>17.45</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>US6174464486</t>
+          <t>US6200763075</t>
         </is>
       </c>
       <c r="B808" t="n">
-        <v>12.22</v>
+        <v>37.89</v>
       </c>
       <c r="C808" t="n">
-        <v>13.82</v>
+        <v>32.5</v>
       </c>
       <c r="D808" t="n">
-        <v>17.99</v>
+        <v>31.53</v>
       </c>
       <c r="E808" t="n">
-        <v>15.82</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>US6200763075</t>
+          <t>US6293775085</t>
         </is>
       </c>
       <c r="B809" t="n">
-        <v>37.89</v>
+        <v>4.83</v>
       </c>
       <c r="C809" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D809" t="n">
-        <v>31.53</v>
-      </c>
+        <v>6.15</v>
+      </c>
+      <c r="D809" t="inlineStr"/>
       <c r="E809" t="n">
-        <v>50.06</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>US6293775085</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="B810" t="n">
-        <v>4.83</v>
+        <v>29.79</v>
       </c>
       <c r="C810" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="D810" t="inlineStr"/>
+        <v>27.15</v>
+      </c>
+      <c r="D810" t="n">
+        <v>27.91</v>
+      </c>
       <c r="E810" t="n">
-        <v>18.08</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>US64110D1046</t>
         </is>
       </c>
       <c r="B811" t="n">
-        <v>29.79</v>
+        <v>23.12</v>
       </c>
       <c r="C811" t="n">
-        <v>27.15</v>
+        <v>17.9</v>
       </c>
       <c r="D811" t="n">
-        <v>27.91</v>
+        <v>10.86</v>
       </c>
       <c r="E811" t="n">
-        <v>40.09</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>US64110D1046</t>
+          <t>US64110L1061</t>
         </is>
       </c>
       <c r="B812" t="n">
-        <v>23.12</v>
+        <v>53.62</v>
       </c>
       <c r="C812" t="n">
-        <v>17.9</v>
+        <v>29.62</v>
       </c>
       <c r="D812" t="n">
-        <v>10.86</v>
+        <v>40.47</v>
       </c>
       <c r="E812" t="n">
-        <v>21.89</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>US64110L1061</t>
+          <t>US6516391066</t>
         </is>
       </c>
       <c r="B813" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="C813" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="D813" t="n">
-        <v>40.47</v>
-      </c>
+        <v>42.6</v>
+      </c>
+      <c r="C813" t="inlineStr"/>
+      <c r="D813" t="inlineStr"/>
       <c r="E813" t="n">
-        <v>44.94</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>US6516391066</t>
+          <t>US6541061031</t>
         </is>
       </c>
       <c r="B814" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="C814" t="inlineStr"/>
-      <c r="D814" t="inlineStr"/>
+        <v>38.35</v>
+      </c>
+      <c r="C814" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="D814" t="n">
+        <v>32.59</v>
+      </c>
       <c r="E814" t="n">
-        <v>13.03</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>US6541061031</t>
+          <t>US6558441084</t>
         </is>
       </c>
       <c r="B815" t="n">
-        <v>38.35</v>
+        <v>24.58</v>
       </c>
       <c r="C815" t="n">
-        <v>31.66</v>
+        <v>17.76</v>
       </c>
       <c r="D815" t="n">
-        <v>32.59</v>
+        <v>29.47</v>
       </c>
       <c r="E815" t="n">
-        <v>25.51</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>US6558441084</t>
+          <t>US6668071029</t>
         </is>
       </c>
       <c r="B816" t="n">
-        <v>24.58</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C816" t="n">
-        <v>17.76</v>
+        <v>17.34</v>
       </c>
       <c r="D816" t="n">
-        <v>29.47</v>
+        <v>34.61</v>
       </c>
       <c r="E816" t="n">
-        <v>20.28</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>US6668071029</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="B817" t="n">
-        <v>8.890000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="C817" t="n">
-        <v>17.34</v>
+        <v>59.37</v>
       </c>
       <c r="D817" t="n">
-        <v>34.61</v>
+        <v>116.91</v>
       </c>
       <c r="E817" t="n">
-        <v>16.56</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US6745991058</t>
         </is>
       </c>
       <c r="B818" t="n">
-        <v>75.3</v>
+        <v>18.38</v>
       </c>
       <c r="C818" t="n">
-        <v>59.37</v>
+        <v>5.08</v>
       </c>
       <c r="D818" t="n">
-        <v>116.91</v>
+        <v>15.29</v>
       </c>
       <c r="E818" t="n">
-        <v>51.14</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>US6745991058</t>
+          <t>US6819191064</t>
         </is>
       </c>
       <c r="B819" t="n">
-        <v>18.38</v>
+        <v>11.22</v>
       </c>
       <c r="C819" t="n">
-        <v>5.08</v>
+        <v>12.83</v>
       </c>
       <c r="D819" t="n">
-        <v>15.29</v>
+        <v>12.52</v>
       </c>
       <c r="E819" t="n">
-        <v>20.21</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>US6819191064</t>
+          <t>US6821891057</t>
         </is>
       </c>
       <c r="B820" t="n">
-        <v>11.22</v>
+        <v>29.86</v>
       </c>
       <c r="C820" t="n">
-        <v>12.83</v>
+        <v>14.68</v>
       </c>
       <c r="D820" t="n">
-        <v>12.52</v>
+        <v>17.08</v>
       </c>
       <c r="E820" t="n">
-        <v>11.54</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>US6821891057</t>
+          <t>US6826801036</t>
         </is>
       </c>
       <c r="B821" t="n">
-        <v>29.86</v>
+        <v>17.54</v>
       </c>
       <c r="C821" t="n">
-        <v>14.68</v>
+        <v>17.12</v>
       </c>
       <c r="D821" t="n">
-        <v>17.08</v>
+        <v>12.82</v>
       </c>
       <c r="E821" t="n">
-        <v>17.35</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>US6826801036</t>
+          <t>US68389X1054</t>
         </is>
       </c>
       <c r="B822" t="n">
-        <v>17.54</v>
+        <v>17.31</v>
       </c>
       <c r="C822" t="n">
-        <v>17.12</v>
+        <v>29.83</v>
       </c>
       <c r="D822" t="n">
-        <v>12.82</v>
+        <v>34.46</v>
       </c>
       <c r="E822" t="n">
-        <v>19.41</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>US68389X1054</t>
+          <t>US68902V1070</t>
         </is>
       </c>
       <c r="B823" t="n">
-        <v>17.31</v>
+        <v>30.15</v>
       </c>
       <c r="C823" t="n">
-        <v>29.83</v>
+        <v>26.44</v>
       </c>
       <c r="D823" t="n">
-        <v>34.46</v>
+        <v>26.38</v>
       </c>
       <c r="E823" t="n">
-        <v>31.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>US68902V1070</t>
-        </is>
-      </c>
-      <c r="B824" t="n">
-        <v>30.15</v>
-      </c>
+          <t>US69331C1080</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr"/>
       <c r="C824" t="n">
-        <v>26.44</v>
+        <v>19.26</v>
       </c>
       <c r="D824" t="n">
-        <v>26.38</v>
+        <v>17.19</v>
       </c>
       <c r="E824" t="n">
-        <v>22.77</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>US69331C1080</t>
-        </is>
-      </c>
-      <c r="B825" t="inlineStr"/>
+          <t>US6934751057</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>15.79</v>
+      </c>
       <c r="C825" t="n">
-        <v>19.26</v>
+        <v>11.4</v>
       </c>
       <c r="D825" t="n">
-        <v>17.19</v>
+        <v>12.11</v>
       </c>
       <c r="E825" t="n">
-        <v>17.51</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>US6934751057</t>
+          <t>US69351T1060</t>
         </is>
       </c>
       <c r="B826" t="n">
-        <v>15.79</v>
+        <v>178.19</v>
       </c>
       <c r="C826" t="n">
-        <v>11.4</v>
+        <v>30.2</v>
       </c>
       <c r="D826" t="n">
-        <v>12.11</v>
+        <v>27.07</v>
       </c>
       <c r="E826" t="n">
-        <v>14.04</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>US69351T1060</t>
+          <t>US69370C1009</t>
         </is>
       </c>
       <c r="B827" t="n">
-        <v>178.19</v>
+        <v>29.73</v>
       </c>
       <c r="C827" t="n">
-        <v>30.2</v>
+        <v>39.5</v>
       </c>
       <c r="D827" t="n">
-        <v>27.07</v>
+        <v>68.86</v>
       </c>
       <c r="E827" t="n">
-        <v>27.11</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>US69370C1009</t>
+          <t>US6937181088</t>
         </is>
       </c>
       <c r="B828" t="n">
-        <v>29.73</v>
+        <v>16.6</v>
       </c>
       <c r="C828" t="n">
-        <v>39.5</v>
+        <v>11.47</v>
       </c>
       <c r="D828" t="n">
-        <v>68.86</v>
+        <v>11.14</v>
       </c>
       <c r="E828" t="n">
-        <v>57.96</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>US6937181088</t>
-        </is>
-      </c>
-      <c r="B829" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="C829" t="n">
-        <v>11.47</v>
-      </c>
+          <t>US6974351057</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr"/>
+      <c r="C829" t="inlineStr"/>
       <c r="D829" t="n">
-        <v>11.14</v>
+        <v>194.58</v>
       </c>
       <c r="E829" t="n">
-        <v>13.16</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>US6974351057</t>
-        </is>
-      </c>
-      <c r="B830" t="inlineStr"/>
-      <c r="C830" t="inlineStr"/>
+          <t>US7010941042</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="C830" t="n">
+        <v>24.38</v>
+      </c>
       <c r="D830" t="n">
-        <v>194.58</v>
+        <v>24.31</v>
       </c>
       <c r="E830" t="n">
-        <v>44.6</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>US7010941042</t>
+          <t>US7043261079</t>
         </is>
       </c>
       <c r="B831" t="n">
-        <v>23.01</v>
+        <v>33.37</v>
       </c>
       <c r="C831" t="n">
-        <v>24.38</v>
+        <v>32.28</v>
       </c>
       <c r="D831" t="n">
-        <v>24.31</v>
+        <v>24.41</v>
       </c>
       <c r="E831" t="n">
-        <v>23.16</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>US7043261079</t>
+          <t>US70450Y1038</t>
         </is>
       </c>
       <c r="B832" t="n">
-        <v>33.37</v>
+        <v>53.65</v>
       </c>
       <c r="C832" t="n">
-        <v>32.28</v>
+        <v>34.09</v>
       </c>
       <c r="D832" t="n">
-        <v>24.41</v>
+        <v>16.01</v>
       </c>
       <c r="E832" t="n">
-        <v>25.74</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>US70450Y1038</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="B833" t="n">
-        <v>53.65</v>
+        <v>30.96</v>
       </c>
       <c r="C833" t="n">
-        <v>34.09</v>
+        <v>28.12</v>
       </c>
       <c r="D833" t="n">
-        <v>16.01</v>
+        <v>25.89</v>
       </c>
       <c r="E833" t="n">
-        <v>21.38</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US7170811035</t>
         </is>
       </c>
       <c r="B834" t="n">
-        <v>30.96</v>
+        <v>15.22</v>
       </c>
       <c r="C834" t="n">
-        <v>28.12</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D834" t="n">
-        <v>25.89</v>
+        <v>76.67</v>
       </c>
       <c r="E834" t="n">
-        <v>21.83</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>US7170811035</t>
+          <t>US7181721090</t>
         </is>
       </c>
       <c r="B835" t="n">
-        <v>15.22</v>
+        <v>16.31</v>
       </c>
       <c r="C835" t="n">
-        <v>9.369999999999999</v>
+        <v>17.41</v>
       </c>
       <c r="D835" t="n">
-        <v>76.67</v>
+        <v>18.75</v>
       </c>
       <c r="E835" t="n">
-        <v>18.86</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>US7181721090</t>
+          <t>US7185461040</t>
         </is>
       </c>
       <c r="B836" t="n">
-        <v>16.31</v>
+        <v>24.43</v>
       </c>
       <c r="C836" t="n">
-        <v>17.41</v>
+        <v>4.47</v>
       </c>
       <c r="D836" t="n">
-        <v>18.75</v>
+        <v>8.6</v>
       </c>
       <c r="E836" t="n">
-        <v>26.62</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>US7185461040</t>
+          <t>US74144T1088</t>
         </is>
       </c>
       <c r="B837" t="n">
-        <v>24.43</v>
+        <v>14.99</v>
       </c>
       <c r="C837" t="n">
-        <v>4.47</v>
+        <v>16.28</v>
       </c>
       <c r="D837" t="n">
-        <v>8.6</v>
+        <v>13.88</v>
       </c>
       <c r="E837" t="n">
-        <v>22.81</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>US74144T1088</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="B838" t="n">
-        <v>14.99</v>
+        <v>24.53</v>
       </c>
       <c r="C838" t="n">
-        <v>16.28</v>
+        <v>24.77</v>
       </c>
       <c r="D838" t="n">
-        <v>13.88</v>
+        <v>25.72</v>
       </c>
       <c r="E838" t="n">
-        <v>12.35</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>US7427181091</t>
-        </is>
-      </c>
-      <c r="B839" t="n">
-        <v>24.53</v>
-      </c>
+          <t>US7445731067</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr"/>
       <c r="C839" t="n">
-        <v>24.77</v>
+        <v>29.77</v>
       </c>
       <c r="D839" t="n">
-        <v>25.72</v>
+        <v>11.93</v>
       </c>
       <c r="E839" t="n">
-        <v>27.4</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>US7445731067</t>
-        </is>
-      </c>
-      <c r="B840" t="inlineStr"/>
+          <t>US7475251036</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>17.01</v>
+      </c>
       <c r="C840" t="n">
-        <v>29.77</v>
+        <v>10.65</v>
       </c>
       <c r="D840" t="n">
-        <v>11.93</v>
+        <v>16.77</v>
       </c>
       <c r="E840" t="n">
-        <v>23.84</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>US7475251036</t>
+          <t>US74967X1037</t>
         </is>
       </c>
       <c r="B841" t="n">
-        <v>17.01</v>
+        <v>47.75</v>
       </c>
       <c r="C841" t="n">
-        <v>10.65</v>
+        <v>17.71</v>
       </c>
       <c r="D841" t="n">
-        <v>16.77</v>
+        <v>15.61</v>
       </c>
       <c r="E841" t="n">
-        <v>18.96</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>US74967X1037</t>
-        </is>
-      </c>
-      <c r="B842" t="n">
-        <v>47.75</v>
-      </c>
+          <t>US7512121010</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr"/>
       <c r="C842" t="n">
-        <v>17.71</v>
+        <v>13.87</v>
       </c>
       <c r="D842" t="n">
-        <v>15.61</v>
+        <v>15.4</v>
       </c>
       <c r="E842" t="n">
-        <v>43.35</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>US7512121010</t>
-        </is>
-      </c>
-      <c r="B843" t="inlineStr"/>
+          <t>US75513E1010</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>33.6</v>
+      </c>
       <c r="C843" t="n">
-        <v>13.87</v>
+        <v>28.85</v>
       </c>
       <c r="D843" t="n">
-        <v>15.4</v>
+        <v>37.8</v>
       </c>
       <c r="E843" t="n">
-        <v>19.32</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>US75513E1010</t>
+          <t>US75886F1075</t>
         </is>
       </c>
       <c r="B844" t="n">
-        <v>33.6</v>
+        <v>8.77</v>
       </c>
       <c r="C844" t="n">
-        <v>28.85</v>
+        <v>18.88</v>
       </c>
       <c r="D844" t="n">
-        <v>37.8</v>
+        <v>25.26</v>
       </c>
       <c r="E844" t="n">
-        <v>32.57</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>US75886F1075</t>
+          <t>US7591EP1005</t>
         </is>
       </c>
       <c r="B845" t="n">
-        <v>8.77</v>
+        <v>8.75</v>
       </c>
       <c r="C845" t="n">
-        <v>18.88</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D845" t="n">
-        <v>25.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E845" t="n">
-        <v>18.58</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>US7591EP1005</t>
+          <t>US7739031091</t>
         </is>
       </c>
       <c r="B846" t="n">
-        <v>8.75</v>
+        <v>25.39</v>
       </c>
       <c r="C846" t="n">
-        <v>9.460000000000001</v>
+        <v>27.01</v>
       </c>
       <c r="D846" t="n">
-        <v>9.199999999999999</v>
+        <v>23.92</v>
       </c>
       <c r="E846" t="n">
-        <v>12.17</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>US7739031091</t>
+          <t>US77543R1023</t>
         </is>
       </c>
       <c r="B847" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="C847" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="D847" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="E847" t="n">
-        <v>32.42</v>
-      </c>
+        <v>133.38</v>
+      </c>
+      <c r="C847" t="inlineStr"/>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>US77543R1023</t>
+          <t>US7782961038</t>
         </is>
       </c>
       <c r="B848" t="n">
-        <v>133.38</v>
-      </c>
-      <c r="C848" t="inlineStr"/>
-      <c r="D848" t="inlineStr"/>
-      <c r="E848" t="inlineStr"/>
+        <v>462.17</v>
+      </c>
+      <c r="C848" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="D848" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="E848" t="n">
+        <v>25.86</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>US7782961038</t>
+          <t>US78409V1044</t>
         </is>
       </c>
       <c r="B849" t="n">
-        <v>462.17</v>
+        <v>37.74</v>
       </c>
       <c r="C849" t="n">
-        <v>19.67</v>
+        <v>32.84</v>
       </c>
       <c r="D849" t="n">
-        <v>27.28</v>
+        <v>53.5</v>
       </c>
       <c r="E849" t="n">
-        <v>25.86</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>US78409V1044</t>
+          <t>US79466L3024</t>
         </is>
       </c>
       <c r="B850" t="n">
-        <v>37.74</v>
+        <v>51.52</v>
       </c>
       <c r="C850" t="n">
-        <v>32.84</v>
+        <v>156.91</v>
       </c>
       <c r="D850" t="n">
-        <v>53.5</v>
+        <v>805.23</v>
       </c>
       <c r="E850" t="n">
-        <v>40.33</v>
+        <v>66.88</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>US79466L3024</t>
+          <t>US8085131055</t>
         </is>
       </c>
       <c r="B851" t="n">
-        <v>51.52</v>
+        <v>29.76</v>
       </c>
       <c r="C851" t="n">
-        <v>156.91</v>
+        <v>23.77</v>
       </c>
       <c r="D851" t="n">
-        <v>805.23</v>
+        <v>27.1</v>
       </c>
       <c r="E851" t="n">
-        <v>66.88</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>US8085131055</t>
+          <t>US8168511090</t>
         </is>
       </c>
       <c r="B852" t="n">
-        <v>29.76</v>
+        <v>33.02</v>
       </c>
       <c r="C852" t="n">
-        <v>23.77</v>
+        <v>23.35</v>
       </c>
       <c r="D852" t="n">
-        <v>27.1</v>
+        <v>15.61</v>
       </c>
       <c r="E852" t="n">
-        <v>24.78</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>US8168511090</t>
+          <t>US81762P1021</t>
         </is>
       </c>
       <c r="B853" t="n">
-        <v>33.02</v>
+        <v>573.42</v>
       </c>
       <c r="C853" t="n">
-        <v>23.35</v>
+        <v>243.12</v>
       </c>
       <c r="D853" t="n">
-        <v>15.61</v>
+        <v>83.91</v>
       </c>
       <c r="E853" t="n">
-        <v>19.87</v>
+        <v>155.06</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>US81762P1021</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="B854" t="n">
-        <v>573.37</v>
+        <v>50.45</v>
       </c>
       <c r="C854" t="n">
-        <v>243.16</v>
+        <v>30.76</v>
       </c>
       <c r="D854" t="n">
-        <v>83.91</v>
+        <v>33.73</v>
       </c>
       <c r="E854" t="n">
-        <v>155.05</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US83088M1027</t>
         </is>
       </c>
       <c r="B855" t="n">
-        <v>50.45</v>
+        <v>18.27</v>
       </c>
       <c r="C855" t="n">
-        <v>30.76</v>
+        <v>10.92</v>
       </c>
       <c r="D855" t="n">
-        <v>33.73</v>
+        <v>16.08</v>
       </c>
       <c r="E855" t="n">
-        <v>32.21</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>US83088M1027</t>
+          <t>US8326964058</t>
         </is>
       </c>
       <c r="B856" t="n">
-        <v>18.27</v>
+        <v>16.81</v>
       </c>
       <c r="C856" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="D856" t="n">
-        <v>16.08</v>
-      </c>
+        <v>23.46</v>
+      </c>
+      <c r="D856" t="inlineStr"/>
       <c r="E856" t="n">
-        <v>26.79</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>US8326964058</t>
+          <t>US8425871071</t>
         </is>
       </c>
       <c r="B857" t="n">
-        <v>16.81</v>
+        <v>30.61</v>
       </c>
       <c r="C857" t="n">
-        <v>23.46</v>
-      </c>
-      <c r="D857" t="inlineStr"/>
+        <v>21.91</v>
+      </c>
+      <c r="D857" t="n">
+        <v>19.36</v>
+      </c>
       <c r="E857" t="n">
-        <v>16.09</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>US8425871071</t>
+          <t>US8447411088</t>
         </is>
       </c>
       <c r="B858" t="n">
-        <v>30.61</v>
+        <v>26.7</v>
       </c>
       <c r="C858" t="n">
-        <v>21.91</v>
+        <v>40.1</v>
       </c>
       <c r="D858" t="n">
-        <v>19.36</v>
+        <v>39.75</v>
       </c>
       <c r="E858" t="n">
-        <v>20.61</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>US8447411088</t>
+          <t>US8522341036</t>
         </is>
       </c>
       <c r="B859" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="C859" t="n">
-        <v>40.1</v>
-      </c>
+        <v>487.36</v>
+      </c>
+      <c r="C859" t="inlineStr"/>
       <c r="D859" t="n">
-        <v>39.75</v>
+        <v>4864.78</v>
       </c>
       <c r="E859" t="n">
-        <v>44.57</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>US8522341036</t>
+          <t>US8552441094</t>
         </is>
       </c>
       <c r="B860" t="n">
-        <v>487.36</v>
-      </c>
-      <c r="C860" t="inlineStr"/>
+        <v>31.88</v>
+      </c>
+      <c r="C860" t="n">
+        <v>29.75</v>
+      </c>
       <c r="D860" t="n">
-        <v>4864.78</v>
+        <v>25.48</v>
       </c>
       <c r="E860" t="n">
-        <v>18.63</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>US8552441094</t>
+          <t>US8636671013</t>
         </is>
       </c>
       <c r="B861" t="n">
-        <v>31.88</v>
+        <v>51.27</v>
       </c>
       <c r="C861" t="n">
-        <v>29.75</v>
+        <v>39.63</v>
       </c>
       <c r="D861" t="n">
-        <v>25.48</v>
+        <v>36.3</v>
       </c>
       <c r="E861" t="n">
-        <v>29.44</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>US8636671013</t>
-        </is>
-      </c>
-      <c r="B862" t="n">
-        <v>51.27</v>
-      </c>
+          <t>US86771W1053</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr"/>
       <c r="C862" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="D862" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E862" t="n">
-        <v>46.39</v>
-      </c>
+        <v>30.36</v>
+      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>US86771W1053</t>
-        </is>
-      </c>
-      <c r="B863" t="inlineStr"/>
+          <t>US86800U3023</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>16.82</v>
+      </c>
       <c r="C863" t="n">
-        <v>30.36</v>
-      </c>
-      <c r="D863" t="inlineStr"/>
-      <c r="E863" t="inlineStr"/>
+        <v>7.59</v>
+      </c>
+      <c r="D863" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E863" t="n">
+        <v>42.75</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>US86800U3023</t>
+          <t>US8716071076</t>
         </is>
       </c>
       <c r="B864" t="n">
-        <v>16.82</v>
+        <v>69.2</v>
       </c>
       <c r="C864" t="n">
-        <v>7.59</v>
+        <v>46.5</v>
       </c>
       <c r="D864" t="n">
-        <v>21.8</v>
+        <v>59.24</v>
       </c>
       <c r="E864" t="n">
-        <v>42.75</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>US8716071076</t>
+          <t>US87165B1035</t>
         </is>
       </c>
       <c r="B865" t="n">
-        <v>69.2</v>
+        <v>6.32</v>
       </c>
       <c r="C865" t="n">
-        <v>46.5</v>
+        <v>5.34</v>
       </c>
       <c r="D865" t="n">
-        <v>59.24</v>
+        <v>7.36</v>
       </c>
       <c r="E865" t="n">
-        <v>35.39</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>US87165B1035</t>
+          <t>US8725401090</t>
         </is>
       </c>
       <c r="B866" t="n">
-        <v>6.32</v>
+        <v>859.6</v>
       </c>
       <c r="C866" t="n">
-        <v>5.34</v>
+        <v>26.43</v>
       </c>
       <c r="D866" t="n">
-        <v>7.36</v>
+        <v>27.58</v>
       </c>
       <c r="E866" t="n">
-        <v>7.6</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>US8725401090</t>
+          <t>US8725901040</t>
         </is>
       </c>
       <c r="B867" t="n">
-        <v>859.6</v>
+        <v>48.12</v>
       </c>
       <c r="C867" t="n">
-        <v>26.43</v>
+        <v>67.86</v>
       </c>
       <c r="D867" t="n">
-        <v>27.58</v>
+        <v>23.14</v>
       </c>
       <c r="E867" t="n">
-        <v>25.26</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>US8725901040</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="B868" t="n">
-        <v>48.12</v>
+        <v>34.73</v>
       </c>
       <c r="C868" t="n">
-        <v>67.86</v>
-      </c>
-      <c r="D868" t="n">
-        <v>23.14</v>
-      </c>
-      <c r="E868" t="n">
-        <v>22.84</v>
-      </c>
+        <v>42.95</v>
+      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US8760301072</t>
         </is>
       </c>
       <c r="B869" t="n">
-        <v>34.73</v>
+        <v>14.47</v>
       </c>
       <c r="C869" t="n">
-        <v>42.95</v>
-      </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D869" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="E869" t="n">
+        <v>12.23</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>US8760301072</t>
+          <t>US87612E1064</t>
         </is>
       </c>
       <c r="B870" t="n">
-        <v>14.47</v>
+        <v>20.96</v>
       </c>
       <c r="C870" t="n">
-        <v>9.720000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="D870" t="n">
-        <v>11.03</v>
+        <v>28.17</v>
       </c>
       <c r="E870" t="n">
-        <v>12.23</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>US87612E1064</t>
+          <t>US8807701029</t>
         </is>
       </c>
       <c r="B871" t="n">
-        <v>20.96</v>
+        <v>29.6</v>
       </c>
       <c r="C871" t="n">
-        <v>15.44</v>
+        <v>20.72</v>
       </c>
       <c r="D871" t="n">
-        <v>28.17</v>
+        <v>39.73</v>
       </c>
       <c r="E871" t="n">
-        <v>16.27</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>US8807701029</t>
+          <t>US88160R1014</t>
         </is>
       </c>
       <c r="B872" t="n">
-        <v>29.6</v>
+        <v>215.99</v>
       </c>
       <c r="C872" t="n">
-        <v>20.72</v>
+        <v>34.02</v>
       </c>
       <c r="D872" t="n">
-        <v>39.73</v>
+        <v>57.73</v>
       </c>
       <c r="E872" t="n">
-        <v>37.92</v>
+        <v>198.13</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>US88160R1014</t>
+          <t>US8825081040</t>
         </is>
       </c>
       <c r="B873" t="n">
-        <v>215.99</v>
+        <v>22.8</v>
       </c>
       <c r="C873" t="n">
-        <v>34.02</v>
+        <v>17.57</v>
       </c>
       <c r="D873" t="n">
-        <v>57.73</v>
+        <v>24.11</v>
       </c>
       <c r="E873" t="n">
-        <v>198.13</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>US8825081040</t>
+          <t>US88339J1051</t>
         </is>
       </c>
       <c r="B874" t="n">
-        <v>22.8</v>
+        <v>331.67</v>
       </c>
       <c r="C874" t="n">
-        <v>17.57</v>
+        <v>419.76</v>
       </c>
       <c r="D874" t="n">
-        <v>24.11</v>
+        <v>201.12</v>
       </c>
       <c r="E874" t="n">
-        <v>36.09</v>
+        <v>150.08</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>US88339J1051</t>
+          <t>US8835561023</t>
         </is>
       </c>
       <c r="B875" t="n">
-        <v>331.67</v>
+        <v>34.29</v>
       </c>
       <c r="C875" t="n">
-        <v>419.76</v>
+        <v>31.22</v>
       </c>
       <c r="D875" t="n">
-        <v>201.12</v>
+        <v>34.35</v>
       </c>
       <c r="E875" t="n">
-        <v>150.08</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>US8835561023</t>
+          <t>US88579Y1010</t>
         </is>
       </c>
       <c r="B876" t="n">
-        <v>34.29</v>
+        <v>17.56</v>
       </c>
       <c r="C876" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="D876" t="n">
-        <v>34.35</v>
-      </c>
+        <v>11.78</v>
+      </c>
+      <c r="D876" t="inlineStr"/>
       <c r="E876" t="n">
-        <v>31.45</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>US88579Y1010</t>
+          <t>US8923561067</t>
         </is>
       </c>
       <c r="B877" t="n">
-        <v>17.56</v>
+        <v>26.52</v>
       </c>
       <c r="C877" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="D877" t="inlineStr"/>
+        <v>23.17</v>
+      </c>
+      <c r="D877" t="n">
+        <v>21.31</v>
+      </c>
       <c r="E877" t="n">
-        <v>17.09</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>US8923561067</t>
+          <t>US89417E1091</t>
         </is>
       </c>
       <c r="B878" t="n">
-        <v>26.52</v>
+        <v>10.79</v>
       </c>
       <c r="C878" t="n">
-        <v>23.17</v>
+        <v>15.93</v>
       </c>
       <c r="D878" t="n">
-        <v>21.31</v>
+        <v>14.9</v>
       </c>
       <c r="E878" t="n">
-        <v>25.77</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>US89417E1091</t>
+          <t>US89832Q1094</t>
         </is>
       </c>
       <c r="B879" t="n">
-        <v>10.79</v>
+        <v>13.1</v>
       </c>
       <c r="C879" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="D879" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="E879" t="n">
-        <v>11.22</v>
-      </c>
+        <v>9.720000000000001</v>
+      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>US89832Q1094</t>
+          <t>US9029733048</t>
         </is>
       </c>
       <c r="B880" t="n">
-        <v>13.1</v>
+        <v>11.01</v>
       </c>
       <c r="C880" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="D880" t="inlineStr"/>
-      <c r="E880" t="inlineStr"/>
+        <v>11.81</v>
+      </c>
+      <c r="D880" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="E880" t="n">
+        <v>12.64</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>US9029733048</t>
-        </is>
-      </c>
-      <c r="B881" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="C881" t="n">
-        <v>11.81</v>
-      </c>
+          <t>US90353T1007</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr"/>
+      <c r="C881" t="inlineStr"/>
       <c r="D881" t="n">
-        <v>13.22</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="E881" t="n">
-        <v>12.64</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>US90353T1007</t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr"/>
-      <c r="C882" t="inlineStr"/>
+          <t>US9078181081</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="C882" t="n">
+        <v>18.46</v>
+      </c>
       <c r="D882" t="n">
-        <v>70.48999999999999</v>
+        <v>23.5</v>
       </c>
       <c r="E882" t="n">
-        <v>13.23</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>US9078181081</t>
-        </is>
-      </c>
-      <c r="B883" t="n">
-        <v>25.31</v>
-      </c>
+          <t>US9100471096</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr"/>
       <c r="C883" t="n">
-        <v>18.46</v>
+        <v>16.89</v>
       </c>
       <c r="D883" t="n">
-        <v>23.5</v>
+        <v>5.23</v>
       </c>
       <c r="E883" t="n">
-        <v>20.57</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>US9100471096</t>
-        </is>
-      </c>
-      <c r="B884" t="inlineStr"/>
+          <t>US9113121068</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>14.6</v>
+      </c>
       <c r="C884" t="n">
-        <v>16.89</v>
+        <v>13.17</v>
       </c>
       <c r="D884" t="n">
-        <v>5.23</v>
+        <v>20.16</v>
       </c>
       <c r="E884" t="n">
-        <v>10.27</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>US9113121068</t>
+          <t>US9113631090</t>
         </is>
       </c>
       <c r="B885" t="n">
-        <v>14.6</v>
+        <v>17.46</v>
       </c>
       <c r="C885" t="n">
-        <v>13.17</v>
+        <v>11.98</v>
       </c>
       <c r="D885" t="n">
-        <v>20.16</v>
+        <v>16.25</v>
       </c>
       <c r="E885" t="n">
-        <v>18.65</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>US9113631090</t>
+          <t>US91324P1021</t>
         </is>
       </c>
       <c r="B886" t="n">
-        <v>17.46</v>
+        <v>27.77</v>
       </c>
       <c r="C886" t="n">
-        <v>11.98</v>
+        <v>25.03</v>
       </c>
       <c r="D886" t="n">
-        <v>16.25</v>
+        <v>22.06</v>
       </c>
       <c r="E886" t="n">
-        <v>18.21</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>US91324P1021</t>
-        </is>
-      </c>
-      <c r="B887" t="n">
-        <v>27.77</v>
-      </c>
+          <t>US9168961038</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr"/>
       <c r="C887" t="n">
-        <v>25.03</v>
-      </c>
-      <c r="D887" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="E887" t="n">
-        <v>32.62</v>
-      </c>
+        <v>216.49</v>
+      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>US9168961038</t>
-        </is>
-      </c>
-      <c r="B888" t="inlineStr"/>
+          <t>US91913Y1001</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>33.08</v>
+      </c>
       <c r="C888" t="n">
-        <v>216.49</v>
-      </c>
-      <c r="D888" t="inlineStr"/>
-      <c r="E888" t="inlineStr"/>
+        <v>4.37</v>
+      </c>
+      <c r="D888" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="E888" t="n">
+        <v>14.29</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>US91913Y1001</t>
+          <t>US9224751084</t>
         </is>
       </c>
       <c r="B889" t="n">
-        <v>33.08</v>
+        <v>116.93</v>
       </c>
       <c r="C889" t="n">
-        <v>4.37</v>
+        <v>89.81</v>
       </c>
       <c r="D889" t="n">
-        <v>5.21</v>
+        <v>56.8</v>
       </c>
       <c r="E889" t="n">
-        <v>14.29</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>US9224751084</t>
+          <t>US92343E1029</t>
         </is>
       </c>
       <c r="B890" t="n">
-        <v>116.93</v>
+        <v>36.28</v>
       </c>
       <c r="C890" t="n">
-        <v>89.81</v>
+        <v>32.93</v>
       </c>
       <c r="D890" t="n">
-        <v>56.8</v>
+        <v>26.07</v>
       </c>
       <c r="E890" t="n">
-        <v>64.5</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>US92343E1029</t>
+          <t>US92343V1044</t>
         </is>
       </c>
       <c r="B891" t="n">
-        <v>36.28</v>
+        <v>9.77</v>
       </c>
       <c r="C891" t="n">
-        <v>32.93</v>
+        <v>7.79</v>
       </c>
       <c r="D891" t="n">
-        <v>26.07</v>
+        <v>13.68</v>
       </c>
       <c r="E891" t="n">
-        <v>25.87</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>US92343V1044</t>
+          <t>US92532F1003</t>
         </is>
       </c>
       <c r="B892" t="n">
-        <v>9.77</v>
+        <v>24.37</v>
       </c>
       <c r="C892" t="n">
-        <v>7.79</v>
+        <v>22.52</v>
       </c>
       <c r="D892" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="E892" t="n">
-        <v>9.65</v>
-      </c>
+        <v>29.28</v>
+      </c>
+      <c r="E892" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>US92532F1003</t>
-        </is>
-      </c>
-      <c r="B893" t="n">
-        <v>24.37</v>
-      </c>
+          <t>US92556V1061</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr"/>
       <c r="C893" t="n">
-        <v>22.52</v>
+        <v>6.52</v>
       </c>
       <c r="D893" t="n">
-        <v>29.28</v>
+        <v>239.07</v>
       </c>
       <c r="E893" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>US92556V1061</t>
-        </is>
-      </c>
-      <c r="B894" t="inlineStr"/>
+          <t>US92826C8394</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>40.59</v>
+      </c>
       <c r="C894" t="n">
-        <v>6.52</v>
+        <v>25.94</v>
       </c>
       <c r="D894" t="n">
-        <v>239.07</v>
-      </c>
-      <c r="E894" t="inlineStr"/>
+        <v>28.23</v>
+      </c>
+      <c r="E894" t="n">
+        <v>28.67</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>US92826C8394</t>
+          <t>US9297401088</t>
         </is>
       </c>
       <c r="B895" t="n">
-        <v>40.59</v>
+        <v>31.16</v>
       </c>
       <c r="C895" t="n">
-        <v>25.94</v>
+        <v>28.82</v>
       </c>
       <c r="D895" t="n">
-        <v>28.23</v>
+        <v>27.95</v>
       </c>
       <c r="E895" t="n">
-        <v>28.67</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>US9297401088</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="B896" t="n">
-        <v>31.16</v>
+        <v>29.61</v>
       </c>
       <c r="C896" t="n">
-        <v>28.82</v>
+        <v>28.68</v>
       </c>
       <c r="D896" t="n">
-        <v>27.95</v>
+        <v>33.68</v>
       </c>
       <c r="E896" t="n">
-        <v>31.38</v>
+        <v>28.79</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US9344231041</t>
         </is>
       </c>
       <c r="B897" t="n">
-        <v>29.61</v>
-      </c>
-      <c r="C897" t="n">
-        <v>28.68</v>
-      </c>
-      <c r="D897" t="n">
-        <v>33.68</v>
-      </c>
-      <c r="E897" t="n">
-        <v>28.79</v>
-      </c>
+        <v>15.39</v>
+      </c>
+      <c r="C897" t="inlineStr"/>
+      <c r="D897" t="inlineStr"/>
+      <c r="E897" t="inlineStr"/>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>US9344231041</t>
+          <t>US94106L1098</t>
         </is>
       </c>
       <c r="B898" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="C898" t="inlineStr"/>
-      <c r="D898" t="inlineStr"/>
-      <c r="E898" t="inlineStr"/>
+        <v>38.87</v>
+      </c>
+      <c r="C898" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="D898" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="E898" t="n">
+        <v>29.64</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>US94106L1098</t>
+          <t>US9497461015</t>
         </is>
       </c>
       <c r="B899" t="n">
-        <v>38.87</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C899" t="n">
-        <v>29.09</v>
+        <v>13.13</v>
       </c>
       <c r="D899" t="n">
-        <v>31.63</v>
+        <v>10.18</v>
       </c>
       <c r="E899" t="n">
-        <v>29.64</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>US9497461015</t>
+          <t>US9581021055</t>
         </is>
       </c>
       <c r="B900" t="n">
-        <v>9.699999999999999</v>
+        <v>26.42</v>
       </c>
       <c r="C900" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="D900" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="E900" t="n">
-        <v>13.09</v>
-      </c>
+        <v>9.15</v>
+      </c>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>US9581021055</t>
+          <t>US9694571004</t>
         </is>
       </c>
       <c r="B901" t="n">
-        <v>26.42</v>
+        <v>20.95</v>
       </c>
       <c r="C901" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="D901" t="inlineStr"/>
-      <c r="E901" t="inlineStr"/>
+        <v>19.66</v>
+      </c>
+      <c r="D901" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="E901" t="n">
+        <v>29.79</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>US9694571004</t>
-        </is>
-      </c>
-      <c r="B902" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="C902" t="n">
-        <v>19.66</v>
-      </c>
+          <t>US9831341071</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr"/>
+      <c r="C902" t="inlineStr"/>
       <c r="D902" t="n">
-        <v>13.41</v>
+        <v>14.41</v>
       </c>
       <c r="E902" t="n">
-        <v>29.79</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>US9831341071</t>
-        </is>
-      </c>
-      <c r="B903" t="inlineStr"/>
-      <c r="C903" t="inlineStr"/>
+          <t>US98389B1008</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="C903" t="n">
+        <v>22.09</v>
+      </c>
       <c r="D903" t="n">
-        <v>14.41</v>
+        <v>19.3</v>
       </c>
       <c r="E903" t="n">
-        <v>19.79</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>US98389B1008</t>
+          <t>US98419M1009</t>
         </is>
       </c>
       <c r="B904" t="n">
-        <v>22.89</v>
+        <v>50.98</v>
       </c>
       <c r="C904" t="n">
-        <v>22.09</v>
+        <v>56.37</v>
       </c>
       <c r="D904" t="n">
-        <v>19.3</v>
+        <v>40.97</v>
       </c>
       <c r="E904" t="n">
-        <v>19.64</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>US98419M1009</t>
+          <t>US9884981013</t>
         </is>
       </c>
       <c r="B905" t="n">
-        <v>50.98</v>
+        <v>26.63</v>
       </c>
       <c r="C905" t="n">
-        <v>56.37</v>
+        <v>28.03</v>
       </c>
       <c r="D905" t="n">
-        <v>40.97</v>
+        <v>23.32</v>
       </c>
       <c r="E905" t="n">
-        <v>31.75</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>US9884981013</t>
+          <t>US9892071054</t>
         </is>
       </c>
       <c r="B906" t="n">
-        <v>26.63</v>
+        <v>38.33</v>
       </c>
       <c r="C906" t="n">
-        <v>28.03</v>
+        <v>29.11</v>
       </c>
       <c r="D906" t="n">
-        <v>23.32</v>
+        <v>47.75</v>
       </c>
       <c r="E906" t="n">
-        <v>25.73</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>US9892071054</t>
+          <t>US98978V1035</t>
         </is>
       </c>
       <c r="B907" t="n">
-        <v>38.33</v>
+        <v>57.11</v>
       </c>
       <c r="C907" t="n">
-        <v>29.11</v>
+        <v>32.61</v>
       </c>
       <c r="D907" t="n">
-        <v>47.75</v>
+        <v>38.92</v>
       </c>
       <c r="E907" t="n">
-        <v>37.95</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>US98978V1035</t>
+          <t>US98980L1017</t>
         </is>
       </c>
       <c r="B908" t="n">
-        <v>57.11</v>
+        <v>165.18</v>
       </c>
       <c r="C908" t="n">
-        <v>32.61</v>
+        <v>34.31</v>
       </c>
       <c r="D908" t="n">
-        <v>38.92</v>
+        <v>220.01</v>
       </c>
       <c r="E908" t="n">
-        <v>29.81</v>
-      </c>
-    </row>
-    <row r="909">
-      <c r="A909" t="inlineStr">
-        <is>
-          <t>US98980L1017</t>
-        </is>
-      </c>
-      <c r="B909" t="n">
-        <v>165.18</v>
-      </c>
-      <c r="C909" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="D909" t="n">
-        <v>220.01</v>
-      </c>
-      <c r="E909" t="n">
         <v>31.27</v>
       </c>
     </row>

--- a/data/kgv_5y_real.xlsx
+++ b/data/kgv_5y_real.xlsx
@@ -6832,7 +6832,9 @@
       <c r="D392" t="n">
         <v>19.66</v>
       </c>
-      <c r="E392" t="inlineStr"/>
+      <c r="E392" t="n">
+        <v>18.86</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -10024,7 +10026,9 @@
       <c r="D586" t="n">
         <v>14.81</v>
       </c>
-      <c r="E586" t="inlineStr"/>
+      <c r="E586" t="n">
+        <v>33.59</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -10158,7 +10162,9 @@
       <c r="D594" t="n">
         <v>134.74</v>
       </c>
-      <c r="E594" t="inlineStr"/>
+      <c r="E594" t="n">
+        <v>12.02</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -11908,7 +11914,9 @@
       <c r="D696" t="n">
         <v>35.89</v>
       </c>
-      <c r="E696" t="inlineStr"/>
+      <c r="E696" t="n">
+        <v>36.82</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -12059,7 +12067,9 @@
       <c r="D705" t="n">
         <v>29.22</v>
       </c>
-      <c r="E705" t="inlineStr"/>
+      <c r="E705" t="n">
+        <v>33.25</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -12123,7 +12133,9 @@
       <c r="D709" t="n">
         <v>27.91</v>
       </c>
-      <c r="E709" t="inlineStr"/>
+      <c r="E709" t="n">
+        <v>37.84</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -12265,7 +12277,9 @@
       <c r="D717" t="n">
         <v>9.6</v>
       </c>
-      <c r="E717" t="inlineStr"/>
+      <c r="E717" t="n">
+        <v>18.79</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -12429,7 +12443,9 @@
       <c r="D727" t="n">
         <v>13.34</v>
       </c>
-      <c r="E727" t="inlineStr"/>
+      <c r="E727" t="n">
+        <v>12.48</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -12548,7 +12564,9 @@
       <c r="D734" t="n">
         <v>81.34999999999999</v>
       </c>
-      <c r="E734" t="inlineStr"/>
+      <c r="E734" t="n">
+        <v>71.95999999999999</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -12599,9 +12617,11 @@
         <v>28.32</v>
       </c>
       <c r="D737" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="E737" t="inlineStr"/>
+        <v>25.05</v>
+      </c>
+      <c r="E737" t="n">
+        <v>18.81</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -12635,7 +12655,9 @@
         <v>16.3</v>
       </c>
       <c r="D739" t="inlineStr"/>
-      <c r="E739" t="inlineStr"/>
+      <c r="E739" t="n">
+        <v>13.58</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -12688,7 +12710,9 @@
       <c r="D742" t="n">
         <v>23.41</v>
       </c>
-      <c r="E742" t="inlineStr"/>
+      <c r="E742" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -13296,7 +13320,9 @@
       <c r="D778" t="n">
         <v>44.94</v>
       </c>
-      <c r="E778" t="inlineStr"/>
+      <c r="E778" t="n">
+        <v>37.06</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -13914,7 +13940,7 @@
         <v>25.86</v>
       </c>
       <c r="E813" t="n">
-        <v>23.28</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="814">
@@ -13968,7 +13994,9 @@
       <c r="D816" t="n">
         <v>24.78</v>
       </c>
-      <c r="E816" t="inlineStr"/>
+      <c r="E816" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -14393,7 +14421,9 @@
       <c r="D841" t="n">
         <v>17.09</v>
       </c>
-      <c r="E841" t="inlineStr"/>
+      <c r="E841" t="n">
+        <v>26.68</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -14408,7 +14438,7 @@
         <v>21.31</v>
       </c>
       <c r="D842" t="n">
-        <v>25.77</v>
+        <v>26.74</v>
       </c>
       <c r="E842" t="inlineStr"/>
     </row>
@@ -14427,7 +14457,9 @@
       <c r="D843" t="n">
         <v>11.22</v>
       </c>
-      <c r="E843" t="inlineStr"/>
+      <c r="E843" t="n">
+        <v>10.58</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -14440,7 +14472,9 @@
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr"/>
-      <c r="E844" t="inlineStr"/>
+      <c r="E844" t="n">
+        <v>12.88</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -14457,7 +14491,9 @@
       <c r="D845" t="n">
         <v>12.64</v>
       </c>
-      <c r="E845" t="inlineStr"/>
+      <c r="E845" t="n">
+        <v>11.55</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -14506,7 +14542,9 @@
       <c r="D848" t="n">
         <v>10.27</v>
       </c>
-      <c r="E848" t="inlineStr"/>
+      <c r="E848" t="n">
+        <v>10.96</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
